--- a/research/traditional_assets/database/data/sweden/sweden_packaging_container.xlsx
+++ b/research/traditional_assets/database/data/sweden/sweden_packaging_container.xlsx
@@ -1284,7 +1284,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1421,22 +1421,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.07251485179629544</v>
+        <v>0.07240120120159507</v>
       </c>
       <c r="C2">
-        <v>2904.722970538513</v>
+        <v>2882.920640031149</v>
       </c>
       <c r="D2">
-        <v>2758.522970538514</v>
+        <v>2767.298640031149</v>
       </c>
       <c r="E2">
-        <v>-779.1</v>
+        <v>-748.522</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>30.578</v>
       </c>
       <c r="G2">
         <v>146.2</v>
@@ -1457,28 +1457,28 @@
         <v>211.3999999999999</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>1.5380734</v>
       </c>
       <c r="N2">
-        <v>211.3999999999999</v>
+        <v>209.8619265999999</v>
       </c>
       <c r="O2">
-        <v>43.54839999999999</v>
+        <v>43.23155687959999</v>
       </c>
       <c r="P2">
-        <v>167.8515999999999</v>
+        <v>166.6303697203999</v>
       </c>
       <c r="Q2">
-        <v>449.4516</v>
+        <v>448.2303697203999</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.07251485179629544</v>
+        <v>0.07272911030464148</v>
       </c>
       <c r="T2">
-        <v>0.6169711731246059</v>
+        <v>0.6219194065737063</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>137.4446759172871</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1503,22 +1503,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.07240120120159507</v>
+        <v>0.07228755060689469</v>
       </c>
       <c r="C3">
-        <v>2882.920640031149</v>
+        <v>2861.174323670988</v>
       </c>
       <c r="D3">
-        <v>2767.298640031149</v>
+        <v>2776.130323670988</v>
       </c>
       <c r="E3">
-        <v>-748.522</v>
+        <v>-717.9440000000001</v>
       </c>
       <c r="F3">
-        <v>30.578</v>
+        <v>61.156</v>
       </c>
       <c r="G3">
         <v>146.2</v>
@@ -1539,28 +1539,28 @@
         <v>211.3999999999999</v>
       </c>
       <c r="M3">
-        <v>1.5380734</v>
+        <v>3.0761468</v>
       </c>
       <c r="N3">
-        <v>209.8619265999999</v>
+        <v>208.3238531999999</v>
       </c>
       <c r="O3">
-        <v>43.23155687959999</v>
+        <v>42.91471375919998</v>
       </c>
       <c r="P3">
-        <v>166.6303697203999</v>
+        <v>165.4091394407999</v>
       </c>
       <c r="Q3">
-        <v>448.2303697203999</v>
+        <v>447.0091394408</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.07272911030464148</v>
+        <v>0.07294774143560684</v>
       </c>
       <c r="T3">
-        <v>0.6219194065737063</v>
+        <v>0.6269686243789107</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>137.4446759172871</v>
+        <v>68.72233795864356</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1585,22 +1585,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.07228755060689469</v>
+        <v>0.07217390001219431</v>
       </c>
       <c r="C4">
-        <v>2861.174323670988</v>
+        <v>2839.484559473421</v>
       </c>
       <c r="D4">
-        <v>2776.130323670988</v>
+        <v>2785.018559473421</v>
       </c>
       <c r="E4">
-        <v>-717.9440000000001</v>
+        <v>-687.366</v>
       </c>
       <c r="F4">
-        <v>61.156</v>
+        <v>91.73399999999999</v>
       </c>
       <c r="G4">
         <v>146.2</v>
@@ -1621,28 +1621,28 @@
         <v>211.3999999999999</v>
       </c>
       <c r="M4">
-        <v>3.0761468</v>
+        <v>4.614220199999999</v>
       </c>
       <c r="N4">
-        <v>208.3238531999999</v>
+        <v>206.7857797999999</v>
       </c>
       <c r="O4">
-        <v>42.91471375919998</v>
+        <v>42.59787063879999</v>
       </c>
       <c r="P4">
-        <v>165.4091394407999</v>
+        <v>164.1879091611999</v>
       </c>
       <c r="Q4">
-        <v>447.0091394408</v>
+        <v>445.7879091611999</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.07294774143560684</v>
+        <v>0.0731708804249426</v>
       </c>
       <c r="T4">
-        <v>0.6269686243789107</v>
+        <v>0.6321219497677276</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>68.72233795864356</v>
+        <v>45.81489197242905</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1667,22 +1667,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.07217390001219431</v>
+        <v>0.07206024941749396</v>
       </c>
       <c r="C5">
-        <v>2839.484559473421</v>
+        <v>2817.851892366147</v>
       </c>
       <c r="D5">
-        <v>2785.018559473421</v>
+        <v>2793.963892366147</v>
       </c>
       <c r="E5">
-        <v>-687.366</v>
+        <v>-656.788</v>
       </c>
       <c r="F5">
-        <v>91.73399999999999</v>
+        <v>122.312</v>
       </c>
       <c r="G5">
         <v>146.2</v>
@@ -1703,28 +1703,28 @@
         <v>211.3999999999999</v>
       </c>
       <c r="M5">
-        <v>4.614220199999999</v>
+        <v>6.152293599999999</v>
       </c>
       <c r="N5">
-        <v>206.7857797999999</v>
+        <v>205.2477063999999</v>
       </c>
       <c r="O5">
-        <v>42.59787063879999</v>
+        <v>42.28102751839999</v>
       </c>
       <c r="P5">
-        <v>164.1879091611999</v>
+        <v>162.9666788815999</v>
       </c>
       <c r="Q5">
-        <v>445.7879091611999</v>
+        <v>444.5666788816</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.0731708804249426</v>
+        <v>0.07339866814322288</v>
       </c>
       <c r="T5">
-        <v>0.6321219497677276</v>
+        <v>0.637382636102145</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>45.81489197242905</v>
+        <v>34.36116897932178</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1749,22 +1749,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.07206024941749396</v>
+        <v>0.07194659882279358</v>
       </c>
       <c r="C6">
-        <v>2817.851892366147</v>
+        <v>2796.276874300547</v>
       </c>
       <c r="D6">
-        <v>2793.963892366147</v>
+        <v>2802.966874300547</v>
       </c>
       <c r="E6">
-        <v>-656.788</v>
+        <v>-626.21</v>
       </c>
       <c r="F6">
-        <v>122.312</v>
+        <v>152.89</v>
       </c>
       <c r="G6">
         <v>146.2</v>
@@ -1785,28 +1785,28 @@
         <v>211.3999999999999</v>
       </c>
       <c r="M6">
-        <v>6.152293599999999</v>
+        <v>7.690366999999999</v>
       </c>
       <c r="N6">
-        <v>205.2477063999999</v>
+        <v>203.7096329999999</v>
       </c>
       <c r="O6">
-        <v>42.28102751839999</v>
+        <v>41.96418439799999</v>
       </c>
       <c r="P6">
-        <v>162.9666788815999</v>
+        <v>161.7454486019999</v>
       </c>
       <c r="Q6">
-        <v>444.5666788816</v>
+        <v>443.3454486019999</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.07339866814322288</v>
+        <v>0.0736312513924143</v>
       </c>
       <c r="T6">
-        <v>0.637382636102145</v>
+        <v>0.6427540737278132</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>34.36116897932178</v>
+        <v>27.48893518345742</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1831,22 +1831,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.07194659882279358</v>
+        <v>0.07183294822809322</v>
       </c>
       <c r="C7">
-        <v>2796.276874300547</v>
+        <v>2774.760064365198</v>
       </c>
       <c r="D7">
-        <v>2802.966874300547</v>
+        <v>2812.028064365198</v>
       </c>
       <c r="E7">
-        <v>-626.21</v>
+        <v>-595.6320000000001</v>
       </c>
       <c r="F7">
-        <v>152.89</v>
+        <v>183.468</v>
       </c>
       <c r="G7">
         <v>146.2</v>
@@ -1867,28 +1867,28 @@
         <v>211.3999999999999</v>
       </c>
       <c r="M7">
-        <v>7.690366999999999</v>
+        <v>9.228440399999998</v>
       </c>
       <c r="N7">
-        <v>203.7096329999999</v>
+        <v>202.1715595999999</v>
       </c>
       <c r="O7">
-        <v>41.96418439799999</v>
+        <v>41.64734127759998</v>
       </c>
       <c r="P7">
-        <v>161.7454486019999</v>
+        <v>160.5242183223999</v>
       </c>
       <c r="Q7">
-        <v>443.3454486019999</v>
+        <v>442.1242183223999</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.0736312513924143</v>
+        <v>0.07386878322137577</v>
       </c>
       <c r="T7">
-        <v>0.6427540737278132</v>
+        <v>0.6482397972604104</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>27.48893518345742</v>
+        <v>22.90744598621452</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1913,22 +1913,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.07183294822809322</v>
+        <v>0.07171929763339285</v>
       </c>
       <c r="C8">
-        <v>2774.760064365198</v>
+        <v>2753.302028901622</v>
       </c>
       <c r="D8">
-        <v>2812.028064365198</v>
+        <v>2821.148028901622</v>
       </c>
       <c r="E8">
-        <v>-595.6320000000001</v>
+        <v>-565.0540000000001</v>
       </c>
       <c r="F8">
-        <v>183.468</v>
+        <v>214.046</v>
       </c>
       <c r="G8">
         <v>146.2</v>
@@ -1949,28 +1949,28 @@
         <v>211.3999999999999</v>
       </c>
       <c r="M8">
-        <v>9.228440399999998</v>
+        <v>10.7665138</v>
       </c>
       <c r="N8">
-        <v>202.1715595999999</v>
+        <v>200.6334861999999</v>
       </c>
       <c r="O8">
-        <v>41.64734127759998</v>
+        <v>41.33049815719999</v>
       </c>
       <c r="P8">
-        <v>160.5242183223999</v>
+        <v>159.3029880427999</v>
       </c>
       <c r="Q8">
-        <v>442.1242183223999</v>
+        <v>440.9029880428</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.07386878322137577</v>
+        <v>0.07411142326171274</v>
       </c>
       <c r="T8">
-        <v>0.6482397972604104</v>
+        <v>0.6538434933420958</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>22.90744598621452</v>
+        <v>19.63495370246959</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1995,22 +1995,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.07171929763339284</v>
+        <v>0.07160564703869249</v>
       </c>
       <c r="C9">
-        <v>2753.302028901624</v>
+        <v>2731.903341622278</v>
       </c>
       <c r="D9">
-        <v>2821.148028901624</v>
+        <v>2830.327341622278</v>
       </c>
       <c r="E9">
-        <v>-565.0540000000001</v>
+        <v>-534.476</v>
       </c>
       <c r="F9">
-        <v>214.046</v>
+        <v>244.624</v>
       </c>
       <c r="G9">
         <v>146.2</v>
@@ -2031,28 +2031,28 @@
         <v>211.3999999999999</v>
       </c>
       <c r="M9">
-        <v>10.7665138</v>
+        <v>12.3045872</v>
       </c>
       <c r="N9">
-        <v>200.6334861999999</v>
+        <v>199.0954127999999</v>
       </c>
       <c r="O9">
-        <v>41.33049815719999</v>
+        <v>41.01365503679999</v>
       </c>
       <c r="P9">
-        <v>159.3029880427999</v>
+        <v>158.0817577632</v>
       </c>
       <c r="Q9">
-        <v>440.9029880428</v>
+        <v>439.6817577632</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.07411142326171274</v>
+        <v>0.07435933808553531</v>
       </c>
       <c r="T9">
-        <v>0.6538434933420958</v>
+        <v>0.6595690089038179</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>19.63495370246959</v>
+        <v>17.18058448966089</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2077,22 +2077,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.07160564703869249</v>
+        <v>0.07149199644399212</v>
       </c>
       <c r="C10">
-        <v>2731.903341622278</v>
+        <v>2710.564583730867</v>
       </c>
       <c r="D10">
-        <v>2830.327341622278</v>
+        <v>2839.566583730867</v>
       </c>
       <c r="E10">
-        <v>-534.476</v>
+        <v>-503.8980000000001</v>
       </c>
       <c r="F10">
-        <v>244.624</v>
+        <v>275.2019999999999</v>
       </c>
       <c r="G10">
         <v>146.2</v>
@@ -2113,28 +2113,28 @@
         <v>211.3999999999999</v>
       </c>
       <c r="M10">
-        <v>12.3045872</v>
+        <v>13.8426606</v>
       </c>
       <c r="N10">
-        <v>199.0954127999999</v>
+        <v>197.5573393999999</v>
       </c>
       <c r="O10">
-        <v>41.01365503679999</v>
+        <v>40.69681191639999</v>
       </c>
       <c r="P10">
-        <v>158.0817577632</v>
+        <v>156.8605274836</v>
       </c>
       <c r="Q10">
-        <v>439.6817577632</v>
+        <v>438.4605274836</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.07435933808553531</v>
+        <v>0.07461270158680453</v>
       </c>
       <c r="T10">
-        <v>0.6595690089038179</v>
+        <v>0.6654203599723909</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>17.18058448966089</v>
+        <v>15.27163065747635</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.07149199644399212</v>
+        <v>0.07137834584929174</v>
       </c>
       <c r="C11">
-        <v>2710.564583730867</v>
+        <v>2689.286344045006</v>
       </c>
       <c r="D11">
-        <v>2839.566583730867</v>
+        <v>2848.866344045006</v>
       </c>
       <c r="E11">
-        <v>-503.8980000000001</v>
+        <v>-473.3200000000001</v>
       </c>
       <c r="F11">
-        <v>275.2019999999999</v>
+        <v>305.78</v>
       </c>
       <c r="G11">
         <v>146.2</v>
@@ -2195,28 +2195,28 @@
         <v>211.3999999999999</v>
       </c>
       <c r="M11">
-        <v>13.8426606</v>
+        <v>15.380734</v>
       </c>
       <c r="N11">
-        <v>197.5573393999999</v>
+        <v>196.0192659999999</v>
       </c>
       <c r="O11">
-        <v>40.69681191639999</v>
+        <v>40.37996879599999</v>
       </c>
       <c r="P11">
-        <v>156.8605274836</v>
+        <v>155.6392972039999</v>
       </c>
       <c r="Q11">
-        <v>438.4605274836</v>
+        <v>437.239297204</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.07461270158680453</v>
+        <v>0.07487169538810194</v>
       </c>
       <c r="T11">
-        <v>0.6654203599723909</v>
+        <v>0.6714017410647101</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>15.27163065747635</v>
+        <v>13.74446759172871</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2241,22 +2241,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.07137834584929174</v>
+        <v>0.07139570525459138</v>
       </c>
       <c r="C12">
-        <v>2689.286344045006</v>
+        <v>2657.283925220887</v>
       </c>
       <c r="D12">
-        <v>2848.866344045006</v>
+        <v>2847.441925220887</v>
       </c>
       <c r="E12">
-        <v>-473.3200000000001</v>
+        <v>-442.7420000000001</v>
       </c>
       <c r="F12">
-        <v>305.78</v>
+        <v>336.3579999999999</v>
       </c>
       <c r="G12">
         <v>146.2</v>
@@ -2277,45 +2277,45 @@
         <v>211.3999999999999</v>
       </c>
       <c r="M12">
-        <v>15.380734</v>
+        <v>17.4233444</v>
       </c>
       <c r="N12">
-        <v>196.0192659999999</v>
+        <v>193.9766555999999</v>
       </c>
       <c r="O12">
-        <v>40.37996879599999</v>
+        <v>39.95919105359999</v>
       </c>
       <c r="P12">
-        <v>155.6392972039999</v>
+        <v>154.0174645463999</v>
       </c>
       <c r="Q12">
-        <v>437.239297204</v>
+        <v>435.6174645464</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.07487169538810194</v>
+        <v>0.07513650927482178</v>
       </c>
       <c r="T12">
-        <v>0.6714017410647101</v>
+        <v>0.6775175352152836</v>
       </c>
       <c r="U12">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V12">
         <v>0.206</v>
       </c>
       <c r="W12">
-        <v>0.0399382</v>
+        <v>0.0411292</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y12">
-        <v>13.74446759172871</v>
+        <v>12.13314706675946</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2323,22 +2323,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.07139570525459138</v>
+        <v>0.071293964659891</v>
       </c>
       <c r="C13">
-        <v>2657.283925220887</v>
+        <v>2635.074556886235</v>
       </c>
       <c r="D13">
-        <v>2847.441925220887</v>
+        <v>2855.810556886236</v>
       </c>
       <c r="E13">
-        <v>-442.7420000000001</v>
+        <v>-412.164</v>
       </c>
       <c r="F13">
-        <v>336.3579999999999</v>
+        <v>366.936</v>
       </c>
       <c r="G13">
         <v>146.2</v>
@@ -2359,28 +2359,28 @@
         <v>211.3999999999999</v>
       </c>
       <c r="M13">
-        <v>17.4233444</v>
+        <v>19.0072848</v>
       </c>
       <c r="N13">
-        <v>193.9766555999999</v>
+        <v>192.3927151999999</v>
       </c>
       <c r="O13">
-        <v>39.95919105359999</v>
+        <v>39.63289933119999</v>
       </c>
       <c r="P13">
-        <v>154.0174645463999</v>
+        <v>152.7598158687999</v>
       </c>
       <c r="Q13">
-        <v>435.6174645464</v>
+        <v>434.3598158688</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.07513650927482178</v>
+        <v>0.07540734165896706</v>
       </c>
       <c r="T13">
-        <v>0.6775175352152836</v>
+        <v>0.683772324687461</v>
       </c>
       <c r="U13">
         <v>0.0518</v>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>12.13314706675946</v>
+        <v>11.12205147786284</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2405,22 +2405,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.071293964659891</v>
+        <v>0.07119222406519064</v>
       </c>
       <c r="C14">
-        <v>2635.074556886235</v>
+        <v>2612.914524365567</v>
       </c>
       <c r="D14">
-        <v>2855.810556886236</v>
+        <v>2864.228524365567</v>
       </c>
       <c r="E14">
-        <v>-412.164</v>
+        <v>-381.5860000000001</v>
       </c>
       <c r="F14">
-        <v>366.936</v>
+        <v>397.514</v>
       </c>
       <c r="G14">
         <v>146.2</v>
@@ -2441,28 +2441,28 @@
         <v>211.3999999999999</v>
       </c>
       <c r="M14">
-        <v>19.0072848</v>
+        <v>20.5912252</v>
       </c>
       <c r="N14">
-        <v>192.3927151999999</v>
+        <v>190.8087747999999</v>
       </c>
       <c r="O14">
-        <v>39.63289933119999</v>
+        <v>39.30660760879999</v>
       </c>
       <c r="P14">
-        <v>152.7598158687999</v>
+        <v>151.5021671911999</v>
       </c>
       <c r="Q14">
-        <v>434.3598158688</v>
+        <v>433.1021671912</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.07540734165896706</v>
+        <v>0.07568440007493177</v>
       </c>
       <c r="T14">
-        <v>0.683772324687461</v>
+        <v>0.6901709024233667</v>
       </c>
       <c r="U14">
         <v>0.0518</v>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>11.12205147786284</v>
+        <v>10.26650905648878</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2487,22 +2487,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.07119222406519064</v>
+        <v>0.07127945547049028</v>
       </c>
       <c r="C15">
-        <v>2612.914524365567</v>
+        <v>2575.116013852321</v>
       </c>
       <c r="D15">
-        <v>2864.228524365567</v>
+        <v>2857.008013852321</v>
       </c>
       <c r="E15">
-        <v>-381.5860000000001</v>
+        <v>-351.008</v>
       </c>
       <c r="F15">
-        <v>397.514</v>
+        <v>428.092</v>
       </c>
       <c r="G15">
         <v>146.2</v>
@@ -2523,45 +2523,45 @@
         <v>211.3999999999999</v>
       </c>
       <c r="M15">
-        <v>20.5912252</v>
+        <v>22.902922</v>
       </c>
       <c r="N15">
-        <v>190.8087747999999</v>
+        <v>188.4970779999999</v>
       </c>
       <c r="O15">
-        <v>39.30660760879999</v>
+        <v>38.83039806799999</v>
       </c>
       <c r="P15">
-        <v>151.5021671911999</v>
+        <v>149.6666799319999</v>
       </c>
       <c r="Q15">
-        <v>433.1021671912</v>
+        <v>431.266679932</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.07568440007493177</v>
+        <v>0.07596790170987242</v>
       </c>
       <c r="T15">
-        <v>0.6901709024233667</v>
+        <v>0.6967182842926654</v>
       </c>
       <c r="U15">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V15">
         <v>0.206</v>
       </c>
       <c r="W15">
-        <v>0.0411292</v>
+        <v>0.042479</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y15">
-        <v>10.26650905648878</v>
+        <v>9.230263282562808</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2569,22 +2569,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.07127945547049028</v>
+        <v>0.0711912128757899</v>
       </c>
       <c r="C16">
-        <v>2575.116013852321</v>
+        <v>2551.842438761918</v>
       </c>
       <c r="D16">
-        <v>2857.008013852321</v>
+        <v>2864.312438761918</v>
       </c>
       <c r="E16">
-        <v>-351.008</v>
+        <v>-320.43</v>
       </c>
       <c r="F16">
-        <v>428.092</v>
+        <v>458.67</v>
       </c>
       <c r="G16">
         <v>146.2</v>
@@ -2605,28 +2605,28 @@
         <v>211.3999999999999</v>
       </c>
       <c r="M16">
-        <v>22.902922</v>
+        <v>24.538845</v>
       </c>
       <c r="N16">
-        <v>188.4970779999999</v>
+        <v>186.8611549999999</v>
       </c>
       <c r="O16">
-        <v>38.83039806799999</v>
+        <v>38.49339792999999</v>
       </c>
       <c r="P16">
-        <v>149.6666799319999</v>
+        <v>148.3677570699999</v>
       </c>
       <c r="Q16">
-        <v>431.266679932</v>
+        <v>429.9677570699999</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.07596790170987242</v>
+        <v>0.07625807397151754</v>
       </c>
       <c r="T16">
-        <v>0.6967182842926654</v>
+        <v>0.7034197222059477</v>
       </c>
       <c r="U16">
         <v>0.0535</v>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>9.230263282562808</v>
+        <v>8.614912397058617</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2651,22 +2651,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.0711912128757899</v>
+        <v>0.07110297028108953</v>
       </c>
       <c r="C17">
-        <v>2551.842438761918</v>
+        <v>2528.606309406901</v>
       </c>
       <c r="D17">
-        <v>2864.312438761918</v>
+        <v>2871.654309406901</v>
       </c>
       <c r="E17">
-        <v>-320.4300000000001</v>
+        <v>-289.852</v>
       </c>
       <c r="F17">
-        <v>458.67</v>
+        <v>489.248</v>
       </c>
       <c r="G17">
         <v>146.2</v>
@@ -2687,28 +2687,28 @@
         <v>211.3999999999999</v>
       </c>
       <c r="M17">
-        <v>24.538845</v>
+        <v>26.174768</v>
       </c>
       <c r="N17">
-        <v>186.8611549999999</v>
+        <v>185.2252319999999</v>
       </c>
       <c r="O17">
-        <v>38.49339792999999</v>
+        <v>38.15639779199999</v>
       </c>
       <c r="P17">
-        <v>148.3677570699999</v>
+        <v>147.0688342079999</v>
       </c>
       <c r="Q17">
-        <v>429.9677570699999</v>
+        <v>428.668834208</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.07625807397151754</v>
+        <v>0.07655515509653515</v>
       </c>
       <c r="T17">
-        <v>0.7034197222059477</v>
+        <v>0.7102807181647843</v>
       </c>
       <c r="U17">
         <v>0.0535</v>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>8.614912397058619</v>
+        <v>8.076480372242456</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2733,22 +2733,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.07110297028108953</v>
+        <v>0.07112271168638917</v>
       </c>
       <c r="C18">
-        <v>2528.606309406901</v>
+        <v>2496.382538717273</v>
       </c>
       <c r="D18">
-        <v>2871.654309406901</v>
+        <v>2870.008538717273</v>
       </c>
       <c r="E18">
-        <v>-289.852</v>
+        <v>-259.274</v>
       </c>
       <c r="F18">
-        <v>489.248</v>
+        <v>519.826</v>
       </c>
       <c r="G18">
         <v>146.2</v>
@@ -2769,45 +2769,45 @@
         <v>211.3999999999999</v>
       </c>
       <c r="M18">
-        <v>26.174768</v>
+        <v>28.2265518</v>
       </c>
       <c r="N18">
-        <v>185.2252319999999</v>
+        <v>183.1734481999999</v>
       </c>
       <c r="O18">
-        <v>38.15639779199999</v>
+        <v>37.73373032919999</v>
       </c>
       <c r="P18">
-        <v>147.0688342079999</v>
+        <v>145.4397178707999</v>
       </c>
       <c r="Q18">
-        <v>428.668834208</v>
+        <v>427.0397178708</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.07655515509653515</v>
+        <v>0.07685939480287851</v>
       </c>
       <c r="T18">
-        <v>0.7102807181647843</v>
+        <v>0.7173070393274484</v>
       </c>
       <c r="U18">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V18">
         <v>0.206</v>
       </c>
       <c r="W18">
-        <v>0.042479</v>
+        <v>0.04311420000000001</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y18">
-        <v>8.076480372242456</v>
+        <v>7.489402230137083</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2815,22 +2815,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.07112271168638917</v>
+        <v>0.0710408210916888</v>
       </c>
       <c r="C19">
-        <v>2496.382538717273</v>
+        <v>2472.643812880598</v>
       </c>
       <c r="D19">
-        <v>2870.008538717273</v>
+        <v>2876.847812880598</v>
       </c>
       <c r="E19">
-        <v>-259.274</v>
+        <v>-228.696</v>
       </c>
       <c r="F19">
-        <v>519.826</v>
+        <v>550.404</v>
       </c>
       <c r="G19">
         <v>146.2</v>
@@ -2851,28 +2851,28 @@
         <v>211.3999999999999</v>
       </c>
       <c r="M19">
-        <v>28.2265518</v>
+        <v>29.8869372</v>
       </c>
       <c r="N19">
-        <v>183.1734481999999</v>
+        <v>181.5130627999999</v>
       </c>
       <c r="O19">
-        <v>37.73373032919999</v>
+        <v>37.39169093679998</v>
       </c>
       <c r="P19">
-        <v>145.4397178707999</v>
+        <v>144.1213718631999</v>
       </c>
       <c r="Q19">
-        <v>427.0397178708</v>
+        <v>425.7213718631999</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.07685939480287851</v>
+        <v>0.07717105498986439</v>
       </c>
       <c r="T19">
-        <v>0.7173070393274484</v>
+        <v>0.7245047341770067</v>
       </c>
       <c r="U19">
         <v>0.0543</v>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>7.489402230137083</v>
+        <v>7.0733243284628</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2897,22 +2897,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.0710408210916888</v>
+        <v>0.07095893049698844</v>
       </c>
       <c r="C20">
-        <v>2472.643812880598</v>
+        <v>2448.937761096176</v>
       </c>
       <c r="D20">
-        <v>2876.847812880598</v>
+        <v>2883.719761096176</v>
       </c>
       <c r="E20">
-        <v>-228.6960000000001</v>
+        <v>-198.1180000000001</v>
       </c>
       <c r="F20">
-        <v>550.4039999999999</v>
+        <v>580.982</v>
       </c>
       <c r="G20">
         <v>146.2</v>
@@ -2933,28 +2933,28 @@
         <v>211.3999999999999</v>
       </c>
       <c r="M20">
-        <v>29.88693719999999</v>
+        <v>31.5473226</v>
       </c>
       <c r="N20">
-        <v>181.5130627999999</v>
+        <v>179.8526773999999</v>
       </c>
       <c r="O20">
-        <v>37.39169093679998</v>
+        <v>37.04965154439999</v>
       </c>
       <c r="P20">
-        <v>144.1213718631999</v>
+        <v>142.8030258555999</v>
       </c>
       <c r="Q20">
-        <v>425.7213718631999</v>
+        <v>424.4030258555999</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.07717105498986439</v>
+        <v>0.07749041049010919</v>
       </c>
       <c r="T20">
-        <v>0.7245047341770067</v>
+        <v>0.731880149887048</v>
       </c>
       <c r="U20">
         <v>0.0543</v>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>7.073324328462802</v>
+        <v>6.70104410064897</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2979,22 +2979,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.07095893049698844</v>
+        <v>0.07087703990228807</v>
       </c>
       <c r="C21">
-        <v>2448.937761096176</v>
+        <v>2425.264618070926</v>
       </c>
       <c r="D21">
-        <v>2883.719761096176</v>
+        <v>2890.624618070926</v>
       </c>
       <c r="E21">
-        <v>-198.1180000000001</v>
+        <v>-167.5400000000001</v>
       </c>
       <c r="F21">
-        <v>580.982</v>
+        <v>611.5599999999999</v>
       </c>
       <c r="G21">
         <v>146.2</v>
@@ -3015,28 +3015,28 @@
         <v>211.3999999999999</v>
       </c>
       <c r="M21">
-        <v>31.5473226</v>
+        <v>33.207708</v>
       </c>
       <c r="N21">
-        <v>179.8526773999999</v>
+        <v>178.1922919999999</v>
       </c>
       <c r="O21">
-        <v>37.04965154439999</v>
+        <v>36.70761215199999</v>
       </c>
       <c r="P21">
-        <v>142.8030258555999</v>
+        <v>141.4846798479999</v>
       </c>
       <c r="Q21">
-        <v>424.4030258555999</v>
+        <v>423.084679848</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.07749041049010919</v>
+        <v>0.07781774987786008</v>
       </c>
       <c r="T21">
-        <v>0.731880149887048</v>
+        <v>0.7394399509898403</v>
       </c>
       <c r="U21">
         <v>0.0543</v>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>6.70104410064897</v>
+        <v>6.365991895616522</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3061,22 +3061,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.07087703990228807</v>
+        <v>0.07096188930758771</v>
       </c>
       <c r="C22">
-        <v>2425.264618070926</v>
+        <v>2387.53289731045</v>
       </c>
       <c r="D22">
-        <v>2890.624618070926</v>
+        <v>2883.47089731045</v>
       </c>
       <c r="E22">
-        <v>-167.5400000000001</v>
+        <v>-136.962</v>
       </c>
       <c r="F22">
-        <v>611.5599999999999</v>
+        <v>642.138</v>
       </c>
       <c r="G22">
         <v>146.2</v>
@@ -3097,45 +3097,45 @@
         <v>211.3999999999999</v>
       </c>
       <c r="M22">
-        <v>33.207708</v>
+        <v>35.5102314</v>
       </c>
       <c r="N22">
-        <v>178.1922919999999</v>
+        <v>175.8897685999999</v>
       </c>
       <c r="O22">
-        <v>36.70761215199999</v>
+        <v>36.23329233159998</v>
       </c>
       <c r="P22">
-        <v>141.4846798479999</v>
+        <v>139.6564762683999</v>
       </c>
       <c r="Q22">
-        <v>423.084679848</v>
+        <v>421.2564762684</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.07781774987786008</v>
+        <v>0.07815337633871861</v>
       </c>
       <c r="T22">
-        <v>0.7394399509898403</v>
+        <v>0.7471911394623234</v>
       </c>
       <c r="U22">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V22">
         <v>0.206</v>
       </c>
       <c r="W22">
-        <v>0.04311420000000001</v>
+        <v>0.0439082</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y22">
-        <v>6.365991895616522</v>
+        <v>5.953213810935625</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3143,22 +3143,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.07096188930758771</v>
+        <v>0.07088793871288732</v>
       </c>
       <c r="C23">
-        <v>2387.53289731045</v>
+        <v>2363.187744445187</v>
       </c>
       <c r="D23">
-        <v>2883.47089731045</v>
+        <v>2889.703744445188</v>
       </c>
       <c r="E23">
-        <v>-136.9620000000001</v>
+        <v>-106.3840000000001</v>
       </c>
       <c r="F23">
-        <v>642.1379999999999</v>
+        <v>672.7159999999999</v>
       </c>
       <c r="G23">
         <v>146.2</v>
@@ -3179,28 +3179,28 @@
         <v>211.3999999999999</v>
       </c>
       <c r="M23">
-        <v>35.5102314</v>
+        <v>37.2011948</v>
       </c>
       <c r="N23">
-        <v>175.8897685999999</v>
+        <v>174.1988051999999</v>
       </c>
       <c r="O23">
-        <v>36.23329233159998</v>
+        <v>35.88495387119999</v>
       </c>
       <c r="P23">
-        <v>139.6564762683999</v>
+        <v>138.3138513287999</v>
       </c>
       <c r="Q23">
-        <v>421.2564762684</v>
+        <v>419.9138513288</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.07815337633871861</v>
+        <v>0.0784976086062658</v>
       </c>
       <c r="T23">
-        <v>0.7471911394623234</v>
+        <v>0.7551410763571779</v>
       </c>
       <c r="U23">
         <v>0.0553</v>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>5.953213810935626</v>
+        <v>5.682613183165826</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.07088793871288732</v>
+        <v>0.07081398811818695</v>
       </c>
       <c r="C24">
-        <v>2363.187744445187</v>
+        <v>2338.869595521014</v>
       </c>
       <c r="D24">
-        <v>2889.703744445188</v>
+        <v>2895.963595521014</v>
       </c>
       <c r="E24">
-        <v>-106.3840000000001</v>
+        <v>-75.80600000000004</v>
       </c>
       <c r="F24">
-        <v>672.7159999999999</v>
+        <v>703.294</v>
       </c>
       <c r="G24">
         <v>146.2</v>
@@ -3261,28 +3261,28 @@
         <v>211.3999999999999</v>
       </c>
       <c r="M24">
-        <v>37.2011948</v>
+        <v>38.8921582</v>
       </c>
       <c r="N24">
-        <v>174.1988051999999</v>
+        <v>172.5078417999999</v>
       </c>
       <c r="O24">
-        <v>35.88495387119999</v>
+        <v>35.53661541079999</v>
       </c>
       <c r="P24">
-        <v>138.3138513287999</v>
+        <v>136.9712263892</v>
       </c>
       <c r="Q24">
-        <v>419.9138513288</v>
+        <v>418.5712263892</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.0784976086062658</v>
+        <v>0.07885078197167138</v>
       </c>
       <c r="T24">
-        <v>0.7551410763571779</v>
+        <v>0.7632975051194313</v>
       </c>
       <c r="U24">
         <v>0.0553</v>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>5.682613183165826</v>
+        <v>5.435543044767312</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3307,22 +3307,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.07081398811818695</v>
+        <v>0.07074003752348659</v>
       </c>
       <c r="C25">
-        <v>2338.869595521014</v>
+        <v>2314.578626411631</v>
       </c>
       <c r="D25">
-        <v>2895.963595521014</v>
+        <v>2902.250626411631</v>
       </c>
       <c r="E25">
-        <v>-75.80600000000004</v>
+        <v>-45.22800000000007</v>
       </c>
       <c r="F25">
-        <v>703.294</v>
+        <v>733.872</v>
       </c>
       <c r="G25">
         <v>146.2</v>
@@ -3343,28 +3343,28 @@
         <v>211.3999999999999</v>
       </c>
       <c r="M25">
-        <v>38.8921582</v>
+        <v>40.5831216</v>
       </c>
       <c r="N25">
-        <v>172.5078417999999</v>
+        <v>170.8168783999999</v>
       </c>
       <c r="O25">
-        <v>35.53661541079999</v>
+        <v>35.18827695039999</v>
       </c>
       <c r="P25">
-        <v>136.9712263892</v>
+        <v>135.6286014495999</v>
       </c>
       <c r="Q25">
-        <v>418.5712263892</v>
+        <v>417.2286014496</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.07885078197167138</v>
+        <v>0.07921324937300867</v>
       </c>
       <c r="T25">
-        <v>0.7632975051194313</v>
+        <v>0.7716685767438493</v>
       </c>
       <c r="U25">
         <v>0.0553</v>
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>5.435543044767312</v>
+        <v>5.209062084568672</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3389,22 +3389,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.07074003752348658</v>
+        <v>0.07066608692878622</v>
       </c>
       <c r="C26">
-        <v>2314.578626411632</v>
+        <v>2290.315014521327</v>
       </c>
       <c r="D26">
-        <v>2902.250626411632</v>
+        <v>2908.565014521327</v>
       </c>
       <c r="E26">
-        <v>-45.22800000000007</v>
+        <v>-14.65000000000009</v>
       </c>
       <c r="F26">
-        <v>733.872</v>
+        <v>764.4499999999999</v>
       </c>
       <c r="G26">
         <v>146.2</v>
@@ -3425,28 +3425,28 @@
         <v>211.3999999999999</v>
       </c>
       <c r="M26">
-        <v>40.5831216</v>
+        <v>42.274085</v>
       </c>
       <c r="N26">
-        <v>170.8168783999999</v>
+        <v>169.1259149999999</v>
       </c>
       <c r="O26">
-        <v>35.18827695039999</v>
+        <v>34.83993848999998</v>
       </c>
       <c r="P26">
-        <v>135.6286014495999</v>
+        <v>134.2859765099999</v>
       </c>
       <c r="Q26">
-        <v>417.2286014496</v>
+        <v>415.88597651</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.07921324937300867</v>
+        <v>0.07958538257171496</v>
       </c>
       <c r="T26">
-        <v>0.7716685767438493</v>
+        <v>0.7802628769449182</v>
       </c>
       <c r="U26">
         <v>0.0553</v>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>5.209062084568672</v>
+        <v>5.000699601185925</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3471,22 +3471,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.07066608692878622</v>
+        <v>0.07059213633408586</v>
       </c>
       <c r="C27">
-        <v>2290.315014521327</v>
+        <v>2266.078938801653</v>
       </c>
       <c r="D27">
-        <v>2908.565014521327</v>
+        <v>2914.906938801653</v>
       </c>
       <c r="E27">
-        <v>-14.65000000000009</v>
+        <v>15.92799999999988</v>
       </c>
       <c r="F27">
-        <v>764.4499999999999</v>
+        <v>795.0279999999999</v>
       </c>
       <c r="G27">
         <v>146.2</v>
@@ -3507,28 +3507,28 @@
         <v>211.3999999999999</v>
       </c>
       <c r="M27">
-        <v>42.274085</v>
+        <v>43.96504839999999</v>
       </c>
       <c r="N27">
-        <v>169.1259149999999</v>
+        <v>167.4349515999999</v>
       </c>
       <c r="O27">
-        <v>34.83993848999998</v>
+        <v>34.49160002959999</v>
       </c>
       <c r="P27">
-        <v>134.2859765099999</v>
+        <v>132.9433515703999</v>
       </c>
       <c r="Q27">
-        <v>415.88597651</v>
+        <v>414.5433515704</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.07958538257171496</v>
+        <v>0.07996757342444034</v>
       </c>
       <c r="T27">
-        <v>0.7802628769449182</v>
+        <v>0.7890894555298001</v>
       </c>
       <c r="U27">
         <v>0.0553</v>
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>5.000699601185925</v>
+        <v>4.808365001140314</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3553,22 +3553,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.07059213633408586</v>
+        <v>0.07051818573938548</v>
       </c>
       <c r="C28">
-        <v>2266.078938801653</v>
+        <v>2241.870579768347</v>
       </c>
       <c r="D28">
-        <v>2914.906938801653</v>
+        <v>2921.276579768347</v>
       </c>
       <c r="E28">
-        <v>15.92799999999988</v>
+        <v>46.50599999999997</v>
       </c>
       <c r="F28">
-        <v>795.0279999999999</v>
+        <v>825.606</v>
       </c>
       <c r="G28">
         <v>146.2</v>
@@ -3589,28 +3589,28 @@
         <v>211.3999999999999</v>
       </c>
       <c r="M28">
-        <v>43.96504839999999</v>
+        <v>45.6560118</v>
       </c>
       <c r="N28">
-        <v>167.4349515999999</v>
+        <v>165.7439881999999</v>
       </c>
       <c r="O28">
-        <v>34.49160002959999</v>
+        <v>34.14326156919999</v>
       </c>
       <c r="P28">
-        <v>132.9433515703999</v>
+        <v>131.6007266308</v>
       </c>
       <c r="Q28">
-        <v>414.5433515704</v>
+        <v>413.2007266308</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.07996757342444034</v>
+        <v>0.08036023525943217</v>
       </c>
       <c r="T28">
-        <v>0.7890894555298001</v>
+        <v>0.7981578581855004</v>
       </c>
       <c r="U28">
         <v>0.0553</v>
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>4.808365001140314</v>
+        <v>4.630277408505487</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3635,22 +3635,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.07051818573938548</v>
+        <v>0.07100003514468511</v>
       </c>
       <c r="C29">
-        <v>2241.870579768347</v>
+        <v>2170.282316119387</v>
       </c>
       <c r="D29">
-        <v>2921.276579768347</v>
+        <v>2880.266316119388</v>
       </c>
       <c r="E29">
-        <v>46.50599999999997</v>
+        <v>77.08399999999995</v>
       </c>
       <c r="F29">
-        <v>825.606</v>
+        <v>856.184</v>
       </c>
       <c r="G29">
         <v>146.2</v>
@@ -3671,45 +3671,45 @@
         <v>211.3999999999999</v>
       </c>
       <c r="M29">
-        <v>45.6560118</v>
+        <v>49.4874352</v>
       </c>
       <c r="N29">
-        <v>165.7439881999999</v>
+        <v>161.9125647999999</v>
       </c>
       <c r="O29">
-        <v>34.14326156919999</v>
+        <v>33.35398834879999</v>
       </c>
       <c r="P29">
-        <v>131.6007266308</v>
+        <v>128.5585764511999</v>
       </c>
       <c r="Q29">
-        <v>413.2007266308</v>
+        <v>410.1585764512</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.08036023525943217</v>
+        <v>0.08076380436761821</v>
       </c>
       <c r="T29">
-        <v>0.7981578581855004</v>
+        <v>0.8074781609149704</v>
       </c>
       <c r="U29">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V29">
         <v>0.206</v>
       </c>
       <c r="W29">
-        <v>0.0439082</v>
+        <v>0.04589320000000001</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y29">
-        <v>4.630277408505487</v>
+        <v>4.271791398071887</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3717,22 +3717,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.07100003514468511</v>
+        <v>0.07094593454998474</v>
       </c>
       <c r="C30">
-        <v>2170.282316119387</v>
+        <v>2144.251351312239</v>
       </c>
       <c r="D30">
-        <v>2880.266316119388</v>
+        <v>2884.813351312239</v>
       </c>
       <c r="E30">
-        <v>77.08399999999995</v>
+        <v>107.662</v>
       </c>
       <c r="F30">
-        <v>856.184</v>
+        <v>886.7620000000001</v>
       </c>
       <c r="G30">
         <v>146.2</v>
@@ -3753,28 +3753,28 @@
         <v>211.3999999999999</v>
       </c>
       <c r="M30">
-        <v>49.4874352</v>
+        <v>51.25484360000001</v>
       </c>
       <c r="N30">
-        <v>161.9125647999999</v>
+        <v>160.1451563999999</v>
       </c>
       <c r="O30">
-        <v>33.35398834879999</v>
+        <v>32.98990221839998</v>
       </c>
       <c r="P30">
-        <v>128.5585764511999</v>
+        <v>127.1552541815999</v>
       </c>
       <c r="Q30">
-        <v>410.1585764512</v>
+        <v>408.7552541816</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.08076380436761821</v>
+        <v>0.08117874161969682</v>
       </c>
       <c r="T30">
-        <v>0.8074781609149704</v>
+        <v>0.8170610073832986</v>
       </c>
       <c r="U30">
         <v>0.0578</v>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>4.271791398071887</v>
+        <v>4.124488246414235</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3799,22 +3799,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.07094593454998474</v>
+        <v>0.07172553395528437</v>
       </c>
       <c r="C31">
-        <v>2144.251351312239</v>
+        <v>2049.506057583596</v>
       </c>
       <c r="D31">
-        <v>2884.813351312239</v>
+        <v>2820.646057583596</v>
       </c>
       <c r="E31">
-        <v>107.6619999999998</v>
+        <v>138.2399999999999</v>
       </c>
       <c r="F31">
-        <v>886.7619999999998</v>
+        <v>917.3399999999999</v>
       </c>
       <c r="G31">
         <v>146.2</v>
@@ -3835,45 +3835,45 @@
         <v>211.3999999999999</v>
       </c>
       <c r="M31">
-        <v>51.25484359999999</v>
+        <v>56.23294199999999</v>
       </c>
       <c r="N31">
-        <v>160.1451563999999</v>
+        <v>155.1670579999999</v>
       </c>
       <c r="O31">
-        <v>32.98990221839999</v>
+        <v>31.96441394799999</v>
       </c>
       <c r="P31">
-        <v>127.1552541815999</v>
+        <v>123.202644052</v>
       </c>
       <c r="Q31">
-        <v>408.7552541816</v>
+        <v>404.802644052</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.08117874161969682</v>
+        <v>0.08160553422183484</v>
       </c>
       <c r="T31">
-        <v>0.8170610073832986</v>
+        <v>0.8269176494650076</v>
       </c>
       <c r="U31">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V31">
         <v>0.206</v>
       </c>
       <c r="W31">
-        <v>0.04589320000000001</v>
+        <v>0.04867220000000001</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y31">
-        <v>4.124488246414236</v>
+        <v>3.759362261359186</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3881,22 +3881,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.07172553395528437</v>
+        <v>0.071699223360584</v>
       </c>
       <c r="C32">
-        <v>2049.506057583596</v>
+        <v>2021.047052433776</v>
       </c>
       <c r="D32">
-        <v>2820.646057583596</v>
+        <v>2822.765052433776</v>
       </c>
       <c r="E32">
-        <v>138.2399999999999</v>
+        <v>168.8179999999999</v>
       </c>
       <c r="F32">
-        <v>917.3399999999999</v>
+        <v>947.9179999999999</v>
       </c>
       <c r="G32">
         <v>146.2</v>
@@ -3917,28 +3917,28 @@
         <v>211.3999999999999</v>
       </c>
       <c r="M32">
-        <v>56.23294199999999</v>
+        <v>58.10737339999999</v>
       </c>
       <c r="N32">
-        <v>155.1670579999999</v>
+        <v>153.2926265999999</v>
       </c>
       <c r="O32">
-        <v>31.96441394799999</v>
+        <v>31.57828107959999</v>
       </c>
       <c r="P32">
-        <v>123.202644052</v>
+        <v>121.7143455203999</v>
       </c>
       <c r="Q32">
-        <v>404.802644052</v>
+        <v>403.3143455204</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.08160553422183484</v>
+        <v>0.0820446976240348</v>
       </c>
       <c r="T32">
-        <v>0.8269176494650076</v>
+        <v>0.8370599913172009</v>
       </c>
       <c r="U32">
         <v>0.0613</v>
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>3.759362261359186</v>
+        <v>3.63809251099276</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3963,22 +3963,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.071699223360584</v>
+        <v>0.07167291276588364</v>
       </c>
       <c r="C33">
-        <v>2021.047052433776</v>
+        <v>1992.591233444012</v>
       </c>
       <c r="D33">
-        <v>2822.765052433776</v>
+        <v>2824.887233444013</v>
       </c>
       <c r="E33">
-        <v>168.8179999999999</v>
+        <v>199.396</v>
       </c>
       <c r="F33">
-        <v>947.9179999999999</v>
+        <v>978.496</v>
       </c>
       <c r="G33">
         <v>146.2</v>
@@ -3999,28 +3999,28 @@
         <v>211.3999999999999</v>
       </c>
       <c r="M33">
-        <v>58.10737339999999</v>
+        <v>59.9818048</v>
       </c>
       <c r="N33">
-        <v>153.2926265999999</v>
+        <v>151.4181951999999</v>
       </c>
       <c r="O33">
-        <v>31.57828107959999</v>
+        <v>31.19214821119999</v>
       </c>
       <c r="P33">
-        <v>121.7143455203999</v>
+        <v>120.2260469887999</v>
       </c>
       <c r="Q33">
-        <v>403.3143455204</v>
+        <v>401.8260469887999</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.0820446976240348</v>
+        <v>0.0824967775968877</v>
       </c>
       <c r="T33">
-        <v>0.8370599913172009</v>
+        <v>0.8475006373415175</v>
       </c>
       <c r="U33">
         <v>0.0613</v>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>3.63809251099276</v>
+        <v>3.524402120024237</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4045,22 +4045,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.07167291276588364</v>
+        <v>0.07238025817118326</v>
       </c>
       <c r="C34">
-        <v>1992.591233444012</v>
+        <v>1906.047877905604</v>
       </c>
       <c r="D34">
-        <v>2824.887233444013</v>
+        <v>2768.921877905604</v>
       </c>
       <c r="E34">
-        <v>199.396</v>
+        <v>229.9739999999999</v>
       </c>
       <c r="F34">
-        <v>978.496</v>
+        <v>1009.074</v>
       </c>
       <c r="G34">
         <v>146.2</v>
@@ -4081,45 +4081,45 @@
         <v>211.3999999999999</v>
       </c>
       <c r="M34">
-        <v>59.9818048</v>
+        <v>64.6816434</v>
       </c>
       <c r="N34">
-        <v>151.4181951999999</v>
+        <v>146.7183565999999</v>
       </c>
       <c r="O34">
-        <v>31.19214821119999</v>
+        <v>30.22398145959999</v>
       </c>
       <c r="P34">
-        <v>120.2260469887999</v>
+        <v>116.4943751403999</v>
       </c>
       <c r="Q34">
-        <v>401.8260469887999</v>
+        <v>398.0943751404</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.0824967775968877</v>
+        <v>0.08296235249430339</v>
       </c>
       <c r="T34">
-        <v>0.8475006373415175</v>
+        <v>0.8582529444411869</v>
       </c>
       <c r="U34">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V34">
         <v>0.206</v>
       </c>
       <c r="W34">
-        <v>0.04867220000000001</v>
+        <v>0.05089540000000001</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y34">
-        <v>3.524402120024237</v>
+        <v>3.26831522651139</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4127,22 +4127,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.07238025817118326</v>
+        <v>0.0723761795764829</v>
       </c>
       <c r="C35">
-        <v>1906.047877905604</v>
+        <v>1875.786220361534</v>
       </c>
       <c r="D35">
-        <v>2768.921877905604</v>
+        <v>2769.238220361534</v>
       </c>
       <c r="E35">
-        <v>229.9739999999999</v>
+        <v>260.552</v>
       </c>
       <c r="F35">
-        <v>1009.074</v>
+        <v>1039.652</v>
       </c>
       <c r="G35">
         <v>146.2</v>
@@ -4163,28 +4163,28 @@
         <v>211.3999999999999</v>
       </c>
       <c r="M35">
-        <v>64.6816434</v>
+        <v>66.64169320000001</v>
       </c>
       <c r="N35">
-        <v>146.7183565999999</v>
+        <v>144.7583067999999</v>
       </c>
       <c r="O35">
-        <v>30.22398145959999</v>
+        <v>29.82021120079998</v>
       </c>
       <c r="P35">
-        <v>116.4943751403999</v>
+        <v>114.9380955991999</v>
       </c>
       <c r="Q35">
-        <v>398.0943751404</v>
+        <v>396.5380955991999</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.08296235249430339</v>
+        <v>0.08344203572194379</v>
       </c>
       <c r="T35">
-        <v>0.8582529444411869</v>
+        <v>0.8693310790287251</v>
       </c>
       <c r="U35">
         <v>0.0641</v>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>3.26831522651139</v>
+        <v>3.172188308084583</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4209,22 +4209,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.0723761795764829</v>
+        <v>0.07237210098178254</v>
       </c>
       <c r="C36">
-        <v>1875.786220361534</v>
+        <v>1845.524635108405</v>
       </c>
       <c r="D36">
-        <v>2769.238220361534</v>
+        <v>2769.554635108405</v>
       </c>
       <c r="E36">
-        <v>260.552</v>
+        <v>291.13</v>
       </c>
       <c r="F36">
-        <v>1039.652</v>
+        <v>1070.23</v>
       </c>
       <c r="G36">
         <v>146.2</v>
@@ -4245,28 +4245,28 @@
         <v>211.3999999999999</v>
       </c>
       <c r="M36">
-        <v>66.64169320000001</v>
+        <v>68.601743</v>
       </c>
       <c r="N36">
-        <v>144.7583067999999</v>
+        <v>142.7982569999999</v>
       </c>
       <c r="O36">
-        <v>29.82021120079998</v>
+        <v>29.41644094199999</v>
       </c>
       <c r="P36">
-        <v>114.9380955991999</v>
+        <v>113.3818160579999</v>
       </c>
       <c r="Q36">
-        <v>396.5380955991999</v>
+        <v>394.9818160579999</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.08344203572194379</v>
+        <v>0.0839364784335116</v>
       </c>
       <c r="T36">
-        <v>0.8693310790287251</v>
+        <v>0.8807500792958798</v>
       </c>
       <c r="U36">
         <v>0.0641</v>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>3.172188308084583</v>
+        <v>3.081554356425024</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.07237210098178254</v>
+        <v>0.07459757438708217</v>
       </c>
       <c r="C37">
-        <v>1845.524635108405</v>
+        <v>1652.409639813004</v>
       </c>
       <c r="D37">
-        <v>2769.554635108405</v>
+        <v>2607.017639813004</v>
       </c>
       <c r="E37">
-        <v>291.13</v>
+        <v>321.708</v>
       </c>
       <c r="F37">
-        <v>1070.23</v>
+        <v>1100.808</v>
       </c>
       <c r="G37">
         <v>146.2</v>
@@ -4327,45 +4327,45 @@
         <v>211.3999999999999</v>
       </c>
       <c r="M37">
-        <v>68.601743</v>
+        <v>79.1480952</v>
       </c>
       <c r="N37">
-        <v>142.7982569999999</v>
+        <v>132.2519047999999</v>
       </c>
       <c r="O37">
-        <v>29.41644094199999</v>
+        <v>27.24389238879998</v>
       </c>
       <c r="P37">
-        <v>113.3818160579999</v>
+        <v>105.0080124111999</v>
       </c>
       <c r="Q37">
-        <v>394.9818160579999</v>
+        <v>386.6080124112</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.0839364784335116</v>
+        <v>0.08444637247981589</v>
       </c>
       <c r="T37">
-        <v>0.8807500792958798</v>
+        <v>0.892525923321383</v>
       </c>
       <c r="U37">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V37">
         <v>0.206</v>
       </c>
       <c r="W37">
-        <v>0.05089540000000001</v>
+        <v>0.05708860000000001</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y37">
-        <v>3.081554356425024</v>
+        <v>2.67094235768797</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4373,22 +4373,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.07459757438708217</v>
+        <v>0.0746554277923818</v>
       </c>
       <c r="C38">
-        <v>1652.409639813004</v>
+        <v>1617.860357963492</v>
       </c>
       <c r="D38">
-        <v>2607.017639813004</v>
+        <v>2603.046357963492</v>
       </c>
       <c r="E38">
-        <v>321.7079999999997</v>
+        <v>352.2859999999999</v>
       </c>
       <c r="F38">
-        <v>1100.808</v>
+        <v>1131.386</v>
       </c>
       <c r="G38">
         <v>146.2</v>
@@ -4409,28 +4409,28 @@
         <v>211.3999999999999</v>
       </c>
       <c r="M38">
-        <v>79.14809519999999</v>
+        <v>81.34665340000001</v>
       </c>
       <c r="N38">
-        <v>132.2519047999999</v>
+        <v>130.0533465999999</v>
       </c>
       <c r="O38">
-        <v>27.24389238879998</v>
+        <v>26.79098939959998</v>
       </c>
       <c r="P38">
-        <v>105.0080124111999</v>
+        <v>103.2623572003999</v>
       </c>
       <c r="Q38">
-        <v>386.6080124112</v>
+        <v>384.8623572004</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.08444637247981589</v>
+        <v>0.08497245363870126</v>
       </c>
       <c r="T38">
-        <v>0.892525923321383</v>
+        <v>0.9046756036651562</v>
       </c>
       <c r="U38">
         <v>0.07190000000000001</v>
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>2.670942357687971</v>
+        <v>2.598754726399106</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4455,22 +4455,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.0746554277923818</v>
+        <v>0.07471328119768143</v>
       </c>
       <c r="C39">
-        <v>1617.860357963492</v>
+        <v>1583.323156655108</v>
       </c>
       <c r="D39">
-        <v>2603.046357963492</v>
+        <v>2599.087156655108</v>
       </c>
       <c r="E39">
-        <v>352.2859999999999</v>
+        <v>382.8639999999999</v>
       </c>
       <c r="F39">
-        <v>1131.386</v>
+        <v>1161.964</v>
       </c>
       <c r="G39">
         <v>146.2</v>
@@ -4491,28 +4491,28 @@
         <v>211.3999999999999</v>
       </c>
       <c r="M39">
-        <v>81.34665340000001</v>
+        <v>83.5452116</v>
       </c>
       <c r="N39">
-        <v>130.0533465999999</v>
+        <v>127.8547883999999</v>
       </c>
       <c r="O39">
-        <v>26.79098939959998</v>
+        <v>26.33808641039998</v>
       </c>
       <c r="P39">
-        <v>103.2623572003999</v>
+        <v>101.5167019895999</v>
       </c>
       <c r="Q39">
-        <v>384.8623572004</v>
+        <v>383.1167019896</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.08497245363870126</v>
+        <v>0.08551550515755069</v>
       </c>
       <c r="T39">
-        <v>0.9046756036651562</v>
+        <v>0.9172172091813093</v>
       </c>
       <c r="U39">
         <v>0.07190000000000001</v>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>2.598754726399106</v>
+        <v>2.530366444125446</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4537,22 +4537,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.07471328119768143</v>
+        <v>0.07597880860298106</v>
       </c>
       <c r="C40">
-        <v>1583.323156655108</v>
+        <v>1469.054912916165</v>
       </c>
       <c r="D40">
-        <v>2599.087156655108</v>
+        <v>2515.396912916166</v>
       </c>
       <c r="E40">
-        <v>382.8639999999999</v>
+        <v>413.4419999999999</v>
       </c>
       <c r="F40">
-        <v>1161.964</v>
+        <v>1192.542</v>
       </c>
       <c r="G40">
         <v>146.2</v>
@@ -4573,45 +4573,45 @@
         <v>211.3999999999999</v>
       </c>
       <c r="M40">
-        <v>83.5452116</v>
+        <v>90.39468360000001</v>
       </c>
       <c r="N40">
-        <v>127.8547883999999</v>
+        <v>121.0053163999999</v>
       </c>
       <c r="O40">
-        <v>26.33808641039998</v>
+        <v>24.92709517839998</v>
       </c>
       <c r="P40">
-        <v>101.5167019895999</v>
+        <v>96.07822122159993</v>
       </c>
       <c r="Q40">
-        <v>383.1167019896</v>
+        <v>377.6782212216</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.08551550515755069</v>
+        <v>0.08607636164423126</v>
       </c>
       <c r="T40">
-        <v>0.9172172091813093</v>
+        <v>0.93017001487832</v>
       </c>
       <c r="U40">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V40">
         <v>0.206</v>
       </c>
       <c r="W40">
-        <v>0.05708860000000001</v>
+        <v>0.06018520000000001</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y40">
-        <v>2.530366444125446</v>
+        <v>2.338633109613538</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4619,22 +4619,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.07597880860298106</v>
+        <v>0.07606762800828069</v>
       </c>
       <c r="C41">
-        <v>1469.054912916165</v>
+        <v>1432.80517097634</v>
       </c>
       <c r="D41">
-        <v>2515.396912916166</v>
+        <v>2509.72517097634</v>
       </c>
       <c r="E41">
-        <v>413.4419999999999</v>
+        <v>444.0199999999999</v>
       </c>
       <c r="F41">
-        <v>1192.542</v>
+        <v>1223.12</v>
       </c>
       <c r="G41">
         <v>146.2</v>
@@ -4655,28 +4655,28 @@
         <v>211.3999999999999</v>
       </c>
       <c r="M41">
-        <v>90.39468360000001</v>
+        <v>92.712496</v>
       </c>
       <c r="N41">
-        <v>121.0053163999999</v>
+        <v>118.6875039999999</v>
       </c>
       <c r="O41">
-        <v>24.92709517839998</v>
+        <v>24.44962582399998</v>
       </c>
       <c r="P41">
-        <v>96.07822122159993</v>
+        <v>94.23787817599994</v>
       </c>
       <c r="Q41">
-        <v>377.6782212216</v>
+        <v>375.8378781759999</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.08607636164423126</v>
+        <v>0.08665591334713449</v>
       </c>
       <c r="T41">
-        <v>0.93017001487832</v>
+        <v>0.9435545807652307</v>
       </c>
       <c r="U41">
         <v>0.07580000000000001</v>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>2.338633109613538</v>
+        <v>2.2801672818732</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4701,22 +4701,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.07606762800828069</v>
+        <v>0.07615644741358032</v>
       </c>
       <c r="C42">
-        <v>1432.80517097634</v>
+        <v>1396.58094889419</v>
       </c>
       <c r="D42">
-        <v>2509.72517097634</v>
+        <v>2504.07894889419</v>
       </c>
       <c r="E42">
-        <v>444.0199999999999</v>
+        <v>474.5980000000001</v>
       </c>
       <c r="F42">
-        <v>1223.12</v>
+        <v>1253.698</v>
       </c>
       <c r="G42">
         <v>146.2</v>
@@ -4737,28 +4737,28 @@
         <v>211.3999999999999</v>
       </c>
       <c r="M42">
-        <v>92.712496</v>
+        <v>95.03030840000001</v>
       </c>
       <c r="N42">
-        <v>118.6875039999999</v>
+        <v>116.3696915999999</v>
       </c>
       <c r="O42">
-        <v>24.44962582399998</v>
+        <v>23.97215646959998</v>
       </c>
       <c r="P42">
-        <v>94.23787817599994</v>
+        <v>92.39753513039993</v>
       </c>
       <c r="Q42">
-        <v>375.8378781759999</v>
+        <v>373.9975351304</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.08665591334713449</v>
+        <v>0.08725511087047513</v>
       </c>
       <c r="T42">
-        <v>0.9435545807652307</v>
+        <v>0.957392860750003</v>
       </c>
       <c r="U42">
         <v>0.07580000000000001</v>
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>2.2801672818732</v>
+        <v>2.224553445729951</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4783,22 +4783,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.07615644741358032</v>
+        <v>0.07624526681887996</v>
       </c>
       <c r="C43">
-        <v>1396.58094889419</v>
+        <v>1360.38207481742</v>
       </c>
       <c r="D43">
-        <v>2504.07894889419</v>
+        <v>2498.45807481742</v>
       </c>
       <c r="E43">
-        <v>474.5980000000001</v>
+        <v>505.176</v>
       </c>
       <c r="F43">
-        <v>1253.698</v>
+        <v>1284.276</v>
       </c>
       <c r="G43">
         <v>146.2</v>
@@ -4819,28 +4819,28 @@
         <v>211.3999999999999</v>
       </c>
       <c r="M43">
-        <v>95.03030840000001</v>
+        <v>97.34812080000002</v>
       </c>
       <c r="N43">
-        <v>116.3696915999999</v>
+        <v>114.0518791999999</v>
       </c>
       <c r="O43">
-        <v>23.97215646959998</v>
+        <v>23.49468711519998</v>
       </c>
       <c r="P43">
-        <v>92.39753513039993</v>
+        <v>90.55719208479992</v>
       </c>
       <c r="Q43">
-        <v>373.9975351304</v>
+        <v>372.1571920847999</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.08725511087047513</v>
+        <v>0.08787497037737924</v>
       </c>
       <c r="T43">
-        <v>0.957392860750003</v>
+        <v>0.9717083228032156</v>
       </c>
       <c r="U43">
         <v>0.07580000000000001</v>
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>2.224553445729951</v>
+        <v>2.171587887498285</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4865,22 +4865,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.07624526681887997</v>
+        <v>0.07633408622417959</v>
       </c>
       <c r="C44">
-        <v>1360.382074817419</v>
+        <v>1324.208378433295</v>
       </c>
       <c r="D44">
-        <v>2498.458074817419</v>
+        <v>2492.862378433295</v>
       </c>
       <c r="E44">
-        <v>505.1759999999998</v>
+        <v>535.7539999999998</v>
       </c>
       <c r="F44">
-        <v>1284.276</v>
+        <v>1314.854</v>
       </c>
       <c r="G44">
         <v>146.2</v>
@@ -4901,28 +4901,28 @@
         <v>211.3999999999999</v>
       </c>
       <c r="M44">
-        <v>97.34812079999999</v>
+        <v>99.6659332</v>
       </c>
       <c r="N44">
-        <v>114.0518791999999</v>
+        <v>111.7340667999999</v>
       </c>
       <c r="O44">
-        <v>23.49468711519999</v>
+        <v>23.01721776079999</v>
       </c>
       <c r="P44">
-        <v>90.55719208479994</v>
+        <v>88.71684903919993</v>
       </c>
       <c r="Q44">
-        <v>372.1571920847999</v>
+        <v>370.3168490392</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.08787497037737924</v>
+        <v>0.08851657934066592</v>
       </c>
       <c r="T44">
-        <v>0.9717083228032155</v>
+        <v>0.9865260817705759</v>
       </c>
       <c r="U44">
         <v>0.07580000000000001</v>
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>2.171587887498286</v>
+        <v>2.121085843602977</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4947,22 +4947,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.07633408622417959</v>
+        <v>0.07642290562947923</v>
       </c>
       <c r="C45">
-        <v>1324.208378433295</v>
+        <v>1288.059690951441</v>
       </c>
       <c r="D45">
-        <v>2492.862378433295</v>
+        <v>2487.291690951441</v>
       </c>
       <c r="E45">
-        <v>535.7539999999998</v>
+        <v>566.3319999999998</v>
       </c>
       <c r="F45">
-        <v>1314.854</v>
+        <v>1345.432</v>
       </c>
       <c r="G45">
         <v>146.2</v>
@@ -4983,28 +4983,28 @@
         <v>211.3999999999999</v>
       </c>
       <c r="M45">
-        <v>99.6659332</v>
+        <v>101.9837456</v>
       </c>
       <c r="N45">
-        <v>111.7340667999999</v>
+        <v>109.4162543999999</v>
       </c>
       <c r="O45">
-        <v>23.01721776079999</v>
+        <v>22.53974840639999</v>
       </c>
       <c r="P45">
-        <v>88.71684903919993</v>
+        <v>86.87650599359995</v>
       </c>
       <c r="Q45">
-        <v>370.3168490392</v>
+        <v>368.4765059936</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.08851657934066592</v>
+        <v>0.08918110290978432</v>
       </c>
       <c r="T45">
-        <v>0.9865260817705759</v>
+        <v>1.001873046415342</v>
       </c>
       <c r="U45">
         <v>0.07580000000000001</v>
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>2.121085843602977</v>
+        <v>2.072879347157455</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5029,22 +5029,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.07642290562947923</v>
+        <v>0.07651172503477885</v>
       </c>
       <c r="C46">
-        <v>1288.059690951441</v>
+        <v>1251.935845086875</v>
       </c>
       <c r="D46">
-        <v>2487.291690951441</v>
+        <v>2481.745845086875</v>
       </c>
       <c r="E46">
-        <v>566.3319999999998</v>
+        <v>596.91</v>
       </c>
       <c r="F46">
-        <v>1345.432</v>
+        <v>1376.01</v>
       </c>
       <c r="G46">
         <v>146.2</v>
@@ -5065,28 +5065,28 @@
         <v>211.3999999999999</v>
       </c>
       <c r="M46">
-        <v>101.9837456</v>
+        <v>104.301558</v>
       </c>
       <c r="N46">
-        <v>109.4162543999999</v>
+        <v>107.0984419999999</v>
       </c>
       <c r="O46">
-        <v>22.53974840639999</v>
+        <v>22.06227905199998</v>
       </c>
       <c r="P46">
-        <v>86.87650599359995</v>
+        <v>85.03616294799993</v>
       </c>
       <c r="Q46">
-        <v>368.4765059936</v>
+        <v>366.6361629479999</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.08918110290978432</v>
+        <v>0.08986979097232517</v>
       </c>
       <c r="T46">
-        <v>1.001873046415342</v>
+        <v>1.017778082501736</v>
       </c>
       <c r="U46">
         <v>0.07580000000000001</v>
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>2.072879347157455</v>
+        <v>2.026815361665066</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5111,22 +5111,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.07651172503477885</v>
+        <v>0.08178695244007848</v>
       </c>
       <c r="C47">
-        <v>1251.935845086875</v>
+        <v>931.1415863498617</v>
       </c>
       <c r="D47">
-        <v>2481.745845086875</v>
+        <v>2191.529586349862</v>
       </c>
       <c r="E47">
-        <v>596.91</v>
+        <v>627.4879999999999</v>
       </c>
       <c r="F47">
-        <v>1376.01</v>
+        <v>1406.588</v>
       </c>
       <c r="G47">
         <v>146.2</v>
@@ -5147,45 +5147,45 @@
         <v>211.3999999999999</v>
       </c>
       <c r="M47">
-        <v>104.301558</v>
+        <v>126.59292</v>
       </c>
       <c r="N47">
-        <v>107.0984419999999</v>
+        <v>84.80707999999993</v>
       </c>
       <c r="O47">
-        <v>22.06227905199998</v>
+        <v>17.47025847999999</v>
       </c>
       <c r="P47">
-        <v>85.03616294799993</v>
+        <v>67.33682151999994</v>
       </c>
       <c r="Q47">
-        <v>366.6361629479999</v>
+        <v>348.93682152</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.08986979097232517</v>
+        <v>0.09058398600014533</v>
       </c>
       <c r="T47">
-        <v>1.017778082501736</v>
+        <v>1.034272193998737</v>
       </c>
       <c r="U47">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V47">
         <v>0.206</v>
       </c>
       <c r="W47">
-        <v>0.06018520000000001</v>
+        <v>0.07146</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y47">
-        <v>2.026815361665066</v>
+        <v>1.669919613197957</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5193,22 +5193,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.08178695244007848</v>
+        <v>0.08198851984537811</v>
       </c>
       <c r="C48">
-        <v>931.1415863498617</v>
+        <v>890.8147079733819</v>
       </c>
       <c r="D48">
-        <v>2191.529586349862</v>
+        <v>2181.780707973382</v>
       </c>
       <c r="E48">
-        <v>627.4879999999999</v>
+        <v>658.0659999999999</v>
       </c>
       <c r="F48">
-        <v>1406.588</v>
+        <v>1437.166</v>
       </c>
       <c r="G48">
         <v>146.2</v>
@@ -5229,28 +5229,28 @@
         <v>211.3999999999999</v>
       </c>
       <c r="M48">
-        <v>126.59292</v>
+        <v>129.34494</v>
       </c>
       <c r="N48">
-        <v>84.80707999999993</v>
+        <v>82.05505999999994</v>
       </c>
       <c r="O48">
-        <v>17.47025847999999</v>
+        <v>16.90334235999999</v>
       </c>
       <c r="P48">
-        <v>67.33682151999994</v>
+        <v>65.15171763999996</v>
       </c>
       <c r="Q48">
-        <v>348.93682152</v>
+        <v>346.75171764</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.09058398600014533</v>
+        <v>0.09132513178373228</v>
       </c>
       <c r="T48">
-        <v>1.034272193998737</v>
+        <v>1.051388724797512</v>
       </c>
       <c r="U48">
         <v>0.09</v>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>1.669919613197957</v>
+        <v>1.634389408661831</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5275,22 +5275,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.08198851984537811</v>
+        <v>0.08219008725067775</v>
       </c>
       <c r="C49">
-        <v>890.8147079733819</v>
+        <v>850.5741799892955</v>
       </c>
       <c r="D49">
-        <v>2181.780707973382</v>
+        <v>2172.118179989296</v>
       </c>
       <c r="E49">
-        <v>658.0659999999999</v>
+        <v>688.6439999999999</v>
       </c>
       <c r="F49">
-        <v>1437.166</v>
+        <v>1467.744</v>
       </c>
       <c r="G49">
         <v>146.2</v>
@@ -5311,28 +5311,28 @@
         <v>211.3999999999999</v>
       </c>
       <c r="M49">
-        <v>129.34494</v>
+        <v>132.09696</v>
       </c>
       <c r="N49">
-        <v>82.05505999999994</v>
+        <v>79.30303999999992</v>
       </c>
       <c r="O49">
-        <v>16.90334235999999</v>
+        <v>16.33642623999999</v>
       </c>
       <c r="P49">
-        <v>65.15171763999996</v>
+        <v>62.96661375999994</v>
       </c>
       <c r="Q49">
-        <v>346.75171764</v>
+        <v>344.5666137599999</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.09132513178373228</v>
+        <v>0.09209478317438027</v>
       </c>
       <c r="T49">
-        <v>1.051388724797512</v>
+        <v>1.069163583703933</v>
       </c>
       <c r="U49">
         <v>0.09</v>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>1.634389408661831</v>
+        <v>1.600339629314709</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.08219008725067775</v>
+        <v>0.08239165465597736</v>
       </c>
       <c r="C50">
-        <v>850.5741799892955</v>
+        <v>810.4188601872081</v>
       </c>
       <c r="D50">
-        <v>2172.118179989296</v>
+        <v>2162.540860187208</v>
       </c>
       <c r="E50">
-        <v>688.6439999999999</v>
+        <v>719.2219999999999</v>
       </c>
       <c r="F50">
-        <v>1467.744</v>
+        <v>1498.322</v>
       </c>
       <c r="G50">
         <v>146.2</v>
@@ -5393,28 +5393,28 @@
         <v>211.3999999999999</v>
       </c>
       <c r="M50">
-        <v>132.09696</v>
+        <v>134.84898</v>
       </c>
       <c r="N50">
-        <v>79.30303999999992</v>
+        <v>76.55101999999994</v>
       </c>
       <c r="O50">
-        <v>16.33642623999999</v>
+        <v>15.76951011999999</v>
       </c>
       <c r="P50">
-        <v>62.96661375999994</v>
+        <v>60.78150987999994</v>
       </c>
       <c r="Q50">
-        <v>344.5666137599999</v>
+        <v>342.38150988</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.09209478317438027</v>
+        <v>0.09289461697250465</v>
       </c>
       <c r="T50">
-        <v>1.069163583703932</v>
+        <v>1.0876354959008</v>
       </c>
       <c r="U50">
         <v>0.09</v>
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>1.600339629314709</v>
+        <v>1.567679636879715</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5439,22 +5439,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.08239165465597736</v>
+        <v>0.08259322206127701</v>
       </c>
       <c r="C51">
-        <v>810.4188601872081</v>
+        <v>770.3476264132571</v>
       </c>
       <c r="D51">
-        <v>2162.540860187208</v>
+        <v>2153.047626413257</v>
       </c>
       <c r="E51">
-        <v>719.2219999999999</v>
+        <v>749.7999999999998</v>
       </c>
       <c r="F51">
-        <v>1498.322</v>
+        <v>1528.9</v>
       </c>
       <c r="G51">
         <v>146.2</v>
@@ -5475,28 +5475,28 @@
         <v>211.3999999999999</v>
       </c>
       <c r="M51">
-        <v>134.84898</v>
+        <v>137.601</v>
       </c>
       <c r="N51">
-        <v>76.55101999999994</v>
+        <v>73.79899999999995</v>
       </c>
       <c r="O51">
-        <v>15.76951011999999</v>
+        <v>15.20259399999999</v>
       </c>
       <c r="P51">
-        <v>60.78150987999994</v>
+        <v>58.59640599999996</v>
       </c>
       <c r="Q51">
-        <v>342.38150988</v>
+        <v>340.196406</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.09289461697250465</v>
+        <v>0.09372644412255401</v>
       </c>
       <c r="T51">
-        <v>1.0876354959008</v>
+        <v>1.106846284585543</v>
       </c>
       <c r="U51">
         <v>0.09</v>
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>1.567679636879715</v>
+        <v>1.536326044142121</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5521,22 +5521,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.08259322206127701</v>
+        <v>0.08279478946657665</v>
       </c>
       <c r="C52">
-        <v>770.3476264132571</v>
+        <v>730.3593761318182</v>
       </c>
       <c r="D52">
-        <v>2153.047626413257</v>
+        <v>2143.637376131818</v>
       </c>
       <c r="E52">
-        <v>749.7999999999998</v>
+        <v>780.3779999999998</v>
       </c>
       <c r="F52">
-        <v>1528.9</v>
+        <v>1559.478</v>
       </c>
       <c r="G52">
         <v>146.2</v>
@@ -5557,28 +5557,28 @@
         <v>211.3999999999999</v>
       </c>
       <c r="M52">
-        <v>137.601</v>
+        <v>140.35302</v>
       </c>
       <c r="N52">
-        <v>73.79899999999995</v>
+        <v>71.04697999999993</v>
       </c>
       <c r="O52">
-        <v>15.20259399999999</v>
+        <v>14.63567787999999</v>
       </c>
       <c r="P52">
-        <v>58.59640599999996</v>
+        <v>56.41130211999995</v>
       </c>
       <c r="Q52">
-        <v>340.196406</v>
+        <v>338.01130212</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.09372644412255401</v>
+        <v>0.09459222340117682</v>
       </c>
       <c r="T52">
-        <v>1.106846284585543</v>
+        <v>1.126841187094153</v>
       </c>
       <c r="U52">
         <v>0.09</v>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>1.536326044142121</v>
+        <v>1.506202004060903</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5603,22 +5603,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.08279478946657665</v>
+        <v>0.1082013788608512</v>
       </c>
       <c r="C53">
-        <v>730.3593761318182</v>
+        <v>-61.66764289425146</v>
       </c>
       <c r="D53">
-        <v>2143.637376131818</v>
+        <v>1382.188357105748</v>
       </c>
       <c r="E53">
-        <v>780.3779999999998</v>
+        <v>810.9559999999998</v>
       </c>
       <c r="F53">
-        <v>1559.478</v>
+        <v>1590.056</v>
       </c>
       <c r="G53">
         <v>146.2</v>
@@ -5639,45 +5639,45 @@
         <v>211.3999999999999</v>
       </c>
       <c r="M53">
-        <v>140.35302</v>
+        <v>233.4202208</v>
       </c>
       <c r="N53">
-        <v>71.04697999999993</v>
+        <v>-22.02022080000006</v>
       </c>
       <c r="O53">
-        <v>14.63567787999999</v>
+        <v>-4.536165484800013</v>
       </c>
       <c r="P53">
-        <v>56.41130211999995</v>
+        <v>-17.48405531520005</v>
       </c>
       <c r="Q53">
-        <v>338.01130212</v>
+        <v>264.1159446848</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.09459222340117682</v>
+        <v>0.09605650268760144</v>
       </c>
       <c r="T53">
-        <v>1.126841187094153</v>
+        <v>1.160658260683636</v>
       </c>
       <c r="U53">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V53">
-        <v>0.206</v>
+        <v>0.186566527316043</v>
       </c>
       <c r="W53">
-        <v>0.07146</v>
+        <v>0.1194120337900049</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y53">
-        <v>1.506202004060903</v>
+        <v>0.9056627539613737</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5685,22 +5685,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1082013788608512</v>
+        <v>0.1092113788608512</v>
       </c>
       <c r="C54">
-        <v>-61.66764289425146</v>
+        <v>-111.4917094418886</v>
       </c>
       <c r="D54">
-        <v>1382.188357105748</v>
+        <v>1362.942290558111</v>
       </c>
       <c r="E54">
-        <v>810.9559999999998</v>
+        <v>841.534</v>
       </c>
       <c r="F54">
-        <v>1590.056</v>
+        <v>1620.634</v>
       </c>
       <c r="G54">
         <v>146.2</v>
@@ -5721,37 +5721,37 @@
         <v>211.3999999999999</v>
       </c>
       <c r="M54">
-        <v>233.4202208</v>
+        <v>237.9090712</v>
       </c>
       <c r="N54">
-        <v>-22.02022080000006</v>
+        <v>-26.50907120000011</v>
       </c>
       <c r="O54">
-        <v>-4.536165484800013</v>
+        <v>-5.460868667200023</v>
       </c>
       <c r="P54">
-        <v>-17.48405531520005</v>
+        <v>-21.04820253280008</v>
       </c>
       <c r="Q54">
-        <v>264.1159446848</v>
+        <v>260.5517974671999</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.09605650268760144</v>
+        <v>0.097125789978827</v>
       </c>
       <c r="T54">
-        <v>1.160658260683636</v>
+        <v>1.185353117293926</v>
       </c>
       <c r="U54">
         <v>0.1468</v>
       </c>
       <c r="V54">
-        <v>0.186566527316043</v>
+        <v>0.1830464041591365</v>
       </c>
       <c r="W54">
-        <v>0.1194120337900049</v>
+        <v>0.1199287878694388</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.9056627539613737</v>
+        <v>0.8885747774715363</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5767,22 +5767,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1092113788608512</v>
+        <v>0.1102213788608512</v>
       </c>
       <c r="C55">
-        <v>-111.4917094418886</v>
+        <v>-160.7871589221772</v>
       </c>
       <c r="D55">
-        <v>1362.942290558111</v>
+        <v>1344.224841077823</v>
       </c>
       <c r="E55">
-        <v>841.534</v>
+        <v>872.112</v>
       </c>
       <c r="F55">
-        <v>1620.634</v>
+        <v>1651.212</v>
       </c>
       <c r="G55">
         <v>146.2</v>
@@ -5803,37 +5803,37 @@
         <v>211.3999999999999</v>
       </c>
       <c r="M55">
-        <v>237.9090712</v>
+        <v>242.3979216</v>
       </c>
       <c r="N55">
-        <v>-26.50907120000011</v>
+        <v>-30.9979216000001</v>
       </c>
       <c r="O55">
-        <v>-5.460868667200023</v>
+        <v>-6.38557184960002</v>
       </c>
       <c r="P55">
-        <v>-21.04820253280008</v>
+        <v>-24.61234975040008</v>
       </c>
       <c r="Q55">
-        <v>260.5517974671999</v>
+        <v>256.9876502495999</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.097125789978827</v>
+        <v>0.09824156802184497</v>
       </c>
       <c r="T55">
-        <v>1.185353117293926</v>
+        <v>1.211121663322055</v>
       </c>
       <c r="U55">
         <v>0.1468</v>
       </c>
       <c r="V55">
-        <v>0.1830464041591365</v>
+        <v>0.1796566559339673</v>
       </c>
       <c r="W55">
-        <v>0.1199287878694388</v>
+        <v>0.1204264029088936</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5841,7 +5841,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.8885747774715363</v>
+        <v>0.8721196889998413</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5849,22 +5849,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1102213788608512</v>
+        <v>0.1112313788608512</v>
       </c>
       <c r="C56">
-        <v>-160.7871589221772</v>
+        <v>-209.5754749818491</v>
       </c>
       <c r="D56">
-        <v>1344.224841077823</v>
+        <v>1326.014525018151</v>
       </c>
       <c r="E56">
-        <v>872.112</v>
+        <v>902.6899999999999</v>
       </c>
       <c r="F56">
-        <v>1651.212</v>
+        <v>1681.79</v>
       </c>
       <c r="G56">
         <v>146.2</v>
@@ -5885,37 +5885,37 @@
         <v>211.3999999999999</v>
       </c>
       <c r="M56">
-        <v>242.3979216</v>
+        <v>246.886772</v>
       </c>
       <c r="N56">
-        <v>-30.9979216000001</v>
+        <v>-35.48677200000009</v>
       </c>
       <c r="O56">
-        <v>-6.38557184960002</v>
+        <v>-7.310275032000018</v>
       </c>
       <c r="P56">
-        <v>-24.61234975040008</v>
+        <v>-28.17649696800007</v>
       </c>
       <c r="Q56">
-        <v>256.9876502495999</v>
+        <v>253.423503032</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.09824156802184497</v>
+        <v>0.09940693620010821</v>
       </c>
       <c r="T56">
-        <v>1.211121663322055</v>
+        <v>1.238035478062545</v>
       </c>
       <c r="U56">
         <v>0.1468</v>
       </c>
       <c r="V56">
-        <v>0.1796566559339673</v>
+        <v>0.1763901712806225</v>
       </c>
       <c r="W56">
-        <v>0.1204264029088936</v>
+        <v>0.1209059228560046</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.8721196889998413</v>
+        <v>0.8562629673816624</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5931,22 +5931,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1112313788608512</v>
+        <v>0.1122413788608513</v>
       </c>
       <c r="C57">
-        <v>-209.5754749818491</v>
+        <v>-257.8769926654579</v>
       </c>
       <c r="D57">
-        <v>1326.014525018151</v>
+        <v>1308.291007334542</v>
       </c>
       <c r="E57">
-        <v>902.6899999999999</v>
+        <v>933.2679999999999</v>
       </c>
       <c r="F57">
-        <v>1681.79</v>
+        <v>1712.368</v>
       </c>
       <c r="G57">
         <v>146.2</v>
@@ -5967,37 +5967,37 @@
         <v>211.3999999999999</v>
       </c>
       <c r="M57">
-        <v>246.886772</v>
+        <v>251.3756224</v>
       </c>
       <c r="N57">
-        <v>-35.48677200000009</v>
+        <v>-39.97562240000011</v>
       </c>
       <c r="O57">
-        <v>-7.310275032000018</v>
+        <v>-8.234978214400023</v>
       </c>
       <c r="P57">
-        <v>-28.17649696800007</v>
+        <v>-31.74064418560008</v>
       </c>
       <c r="Q57">
-        <v>253.423503032</v>
+        <v>249.8593558143999</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.09940693620010821</v>
+        <v>0.1006252756592016</v>
       </c>
       <c r="T57">
-        <v>1.238035478062545</v>
+        <v>1.266172648018512</v>
       </c>
       <c r="U57">
         <v>0.1468</v>
       </c>
       <c r="V57">
-        <v>0.1763901712806225</v>
+        <v>0.1732403467934685</v>
       </c>
       <c r="W57">
-        <v>0.1209059228560046</v>
+        <v>0.1213683170907188</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.8562629673816624</v>
+        <v>0.8409725572498469</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6013,22 +6013,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1122413788608513</v>
+        <v>0.1132513788608513</v>
       </c>
       <c r="C58">
-        <v>-257.8769926654579</v>
+        <v>-305.7109741640379</v>
       </c>
       <c r="D58">
-        <v>1308.291007334542</v>
+        <v>1291.035025835962</v>
       </c>
       <c r="E58">
-        <v>933.2679999999999</v>
+        <v>963.8460000000001</v>
       </c>
       <c r="F58">
-        <v>1712.368</v>
+        <v>1742.946</v>
       </c>
       <c r="G58">
         <v>146.2</v>
@@ -6049,37 +6049,37 @@
         <v>211.3999999999999</v>
       </c>
       <c r="M58">
-        <v>251.3756224</v>
+        <v>255.8644728</v>
       </c>
       <c r="N58">
-        <v>-39.97562240000011</v>
+        <v>-44.46447280000012</v>
       </c>
       <c r="O58">
-        <v>-8.234978214400023</v>
+        <v>-9.159681396800027</v>
       </c>
       <c r="P58">
-        <v>-31.74064418560008</v>
+        <v>-35.3047914032001</v>
       </c>
       <c r="Q58">
-        <v>249.8593558143999</v>
+        <v>246.2952085967999</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1006252756592016</v>
+        <v>0.1019002820698807</v>
       </c>
       <c r="T58">
-        <v>1.266172648018512</v>
+        <v>1.295618523553826</v>
       </c>
       <c r="U58">
         <v>0.1468</v>
       </c>
       <c r="V58">
-        <v>0.1732403467934685</v>
+        <v>0.1702010424637585</v>
       </c>
       <c r="W58">
-        <v>0.1213683170907188</v>
+        <v>0.1218144869663203</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.8409725572498469</v>
+        <v>0.8262186527366917</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6095,22 +6095,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1132513788608513</v>
+        <v>0.1142613788608512</v>
       </c>
       <c r="C59">
-        <v>-305.7109741640379</v>
+        <v>-353.0956786471854</v>
       </c>
       <c r="D59">
-        <v>1291.035025835962</v>
+        <v>1274.228321352815</v>
       </c>
       <c r="E59">
-        <v>963.8460000000001</v>
+        <v>994.4240000000001</v>
       </c>
       <c r="F59">
-        <v>1742.946</v>
+        <v>1773.524</v>
       </c>
       <c r="G59">
         <v>146.2</v>
@@ -6131,37 +6131,37 @@
         <v>211.3999999999999</v>
       </c>
       <c r="M59">
-        <v>255.8644728</v>
+        <v>260.3533232</v>
       </c>
       <c r="N59">
-        <v>-44.46447280000012</v>
+        <v>-48.95332320000011</v>
       </c>
       <c r="O59">
-        <v>-9.159681396800027</v>
+        <v>-10.08438457920002</v>
       </c>
       <c r="P59">
-        <v>-35.3047914032001</v>
+        <v>-38.86893862080009</v>
       </c>
       <c r="Q59">
-        <v>246.2952085967999</v>
+        <v>242.7310613791999</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1019002820698807</v>
+        <v>0.1032360030715445</v>
       </c>
       <c r="T59">
-        <v>1.295618523553826</v>
+        <v>1.326466583638441</v>
       </c>
       <c r="U59">
         <v>0.1468</v>
       </c>
       <c r="V59">
-        <v>0.1702010424637585</v>
+        <v>0.1672665417316247</v>
       </c>
       <c r="W59">
-        <v>0.1218144869663203</v>
+        <v>0.1222452716737975</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.8262186527366917</v>
+        <v>0.8119735035515763</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6177,22 +6177,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1142613788608512</v>
+        <v>0.1478283581802602</v>
       </c>
       <c r="C60">
-        <v>-353.0956786471845</v>
+        <v>-768.4806778664872</v>
       </c>
       <c r="D60">
-        <v>1274.228321352815</v>
+        <v>889.4213221335125</v>
       </c>
       <c r="E60">
-        <v>994.4239999999996</v>
+        <v>1025.001999999999</v>
       </c>
       <c r="F60">
-        <v>1773.524</v>
+        <v>1804.102</v>
       </c>
       <c r="G60">
         <v>146.2</v>
@@ -6213,45 +6213,45 @@
         <v>211.3999999999999</v>
       </c>
       <c r="M60">
-        <v>260.3533232</v>
+        <v>362.2636815999999</v>
       </c>
       <c r="N60">
-        <v>-48.95332320000006</v>
+        <v>-150.8636816</v>
       </c>
       <c r="O60">
-        <v>-10.08438457920001</v>
+        <v>-31.0779184096</v>
       </c>
       <c r="P60">
-        <v>-38.86893862080004</v>
+        <v>-119.7857631904</v>
       </c>
       <c r="Q60">
-        <v>242.7310613792</v>
+        <v>161.8142368096</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1032360030715445</v>
+        <v>0.1063368307547748</v>
       </c>
       <c r="T60">
-        <v>1.326466583638441</v>
+        <v>1.398079232211889</v>
       </c>
       <c r="U60">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V60">
-        <v>0.1672665417316248</v>
+        <v>0.1202118849111812</v>
       </c>
       <c r="W60">
-        <v>0.1222452716737975</v>
+        <v>0.1766614535098348</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y60">
-        <v>0.8119735035515765</v>
+        <v>0.5835528393746661</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6259,22 +6259,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1478283581802602</v>
+        <v>0.1493783581802602</v>
       </c>
       <c r="C61">
-        <v>-768.4806778664872</v>
+        <v>-811.2909837155414</v>
       </c>
       <c r="D61">
-        <v>889.4213221335125</v>
+        <v>877.1890162844585</v>
       </c>
       <c r="E61">
-        <v>1025.001999999999</v>
+        <v>1055.58</v>
       </c>
       <c r="F61">
-        <v>1804.102</v>
+        <v>1834.68</v>
       </c>
       <c r="G61">
         <v>146.2</v>
@@ -6295,37 +6295,37 @@
         <v>211.3999999999999</v>
       </c>
       <c r="M61">
-        <v>362.2636815999999</v>
+        <v>368.403744</v>
       </c>
       <c r="N61">
-        <v>-150.8636816</v>
+        <v>-157.003744</v>
       </c>
       <c r="O61">
-        <v>-31.0779184096</v>
+        <v>-32.34277126400001</v>
       </c>
       <c r="P61">
-        <v>-119.7857631904</v>
+        <v>-124.660972736</v>
       </c>
       <c r="Q61">
-        <v>161.8142368096</v>
+        <v>156.939027264</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1063368307547748</v>
+        <v>0.1078502515236442</v>
       </c>
       <c r="T61">
-        <v>1.398079232211889</v>
+        <v>1.433031213017187</v>
       </c>
       <c r="U61">
         <v>0.2008</v>
       </c>
       <c r="V61">
-        <v>0.1202118849111812</v>
+        <v>0.1182083534959949</v>
       </c>
       <c r="W61">
-        <v>0.1766614535098348</v>
+        <v>0.1770637626180042</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.5835528393746661</v>
+        <v>0.5738269587184215</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6341,22 +6341,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1493783581802602</v>
+        <v>0.1509283581802602</v>
       </c>
       <c r="C62">
-        <v>-811.2909837155414</v>
+        <v>-853.7693898156429</v>
       </c>
       <c r="D62">
-        <v>877.1890162844585</v>
+        <v>865.288610184357</v>
       </c>
       <c r="E62">
-        <v>1055.58</v>
+        <v>1086.158</v>
       </c>
       <c r="F62">
-        <v>1834.68</v>
+        <v>1865.258</v>
       </c>
       <c r="G62">
         <v>146.2</v>
@@ -6377,37 +6377,37 @@
         <v>211.3999999999999</v>
       </c>
       <c r="M62">
-        <v>368.403744</v>
+        <v>374.5438064</v>
       </c>
       <c r="N62">
-        <v>-157.003744</v>
+        <v>-163.1438064000001</v>
       </c>
       <c r="O62">
-        <v>-32.34277126400001</v>
+        <v>-33.60762411840002</v>
       </c>
       <c r="P62">
-        <v>-124.660972736</v>
+        <v>-129.5361822816</v>
       </c>
       <c r="Q62">
-        <v>156.939027264</v>
+        <v>152.0638177184</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1078502515236442</v>
+        <v>0.109441283613994</v>
       </c>
       <c r="T62">
-        <v>1.433031213017187</v>
+        <v>1.46977560309455</v>
       </c>
       <c r="U62">
         <v>0.2008</v>
       </c>
       <c r="V62">
-        <v>0.1182083534959949</v>
+        <v>0.1162705116354047</v>
       </c>
       <c r="W62">
-        <v>0.1770637626180042</v>
+        <v>0.1774528812636107</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.5738269587184215</v>
+        <v>0.5644199593951686</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1509283581802602</v>
+        <v>0.1524783581802602</v>
       </c>
       <c r="C63">
-        <v>-853.7693898156429</v>
+        <v>-895.9292235386997</v>
       </c>
       <c r="D63">
-        <v>865.288610184357</v>
+        <v>853.7067764613001</v>
       </c>
       <c r="E63">
-        <v>1086.158</v>
+        <v>1116.736</v>
       </c>
       <c r="F63">
-        <v>1865.258</v>
+        <v>1895.836</v>
       </c>
       <c r="G63">
         <v>146.2</v>
@@ -6459,37 +6459,37 @@
         <v>211.3999999999999</v>
       </c>
       <c r="M63">
-        <v>374.5438064</v>
+        <v>380.6838688</v>
       </c>
       <c r="N63">
-        <v>-163.1438064000001</v>
+        <v>-169.2838688000001</v>
       </c>
       <c r="O63">
-        <v>-33.60762411840002</v>
+        <v>-34.87247697280002</v>
       </c>
       <c r="P63">
-        <v>-129.5361822816</v>
+        <v>-134.4113918272</v>
       </c>
       <c r="Q63">
-        <v>152.0638177184</v>
+        <v>147.1886081728</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.109441283613994</v>
+        <v>0.1111160542354149</v>
       </c>
       <c r="T63">
-        <v>1.46977560309455</v>
+        <v>1.508453908439144</v>
       </c>
       <c r="U63">
         <v>0.2008</v>
       </c>
       <c r="V63">
-        <v>0.1162705116354047</v>
+        <v>0.1143951808025757</v>
       </c>
       <c r="W63">
-        <v>0.1774528812636107</v>
+        <v>0.1778294476948428</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.5644199593951686</v>
+        <v>0.5553164116629885</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6505,22 +6505,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1524783581802602</v>
+        <v>0.1540283581802602</v>
       </c>
       <c r="C64">
-        <v>-895.9292235386997</v>
+        <v>-937.7831081370693</v>
       </c>
       <c r="D64">
-        <v>853.7067764613001</v>
+        <v>842.4308918629305</v>
       </c>
       <c r="E64">
-        <v>1116.736</v>
+        <v>1147.314</v>
       </c>
       <c r="F64">
-        <v>1895.836</v>
+        <v>1926.414</v>
       </c>
       <c r="G64">
         <v>146.2</v>
@@ -6541,37 +6541,37 @@
         <v>211.3999999999999</v>
       </c>
       <c r="M64">
-        <v>380.6838688</v>
+        <v>386.8239311999999</v>
       </c>
       <c r="N64">
-        <v>-169.2838688000001</v>
+        <v>-175.4239312</v>
       </c>
       <c r="O64">
-        <v>-34.87247697280002</v>
+        <v>-36.13732982720001</v>
       </c>
       <c r="P64">
-        <v>-134.4113918272</v>
+        <v>-139.2866013728</v>
       </c>
       <c r="Q64">
-        <v>147.1886081728</v>
+        <v>142.3133986272</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1111160542354149</v>
+        <v>0.1128813529985342</v>
       </c>
       <c r="T64">
-        <v>1.508453908439144</v>
+        <v>1.549222932991553</v>
       </c>
       <c r="U64">
         <v>0.2008</v>
       </c>
       <c r="V64">
-        <v>0.1143951808025757</v>
+        <v>0.1125793842818999</v>
       </c>
       <c r="W64">
-        <v>0.1778294476948428</v>
+        <v>0.1781940596361945</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.5553164116629885</v>
+        <v>0.5465018654461158</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6587,22 +6587,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1540283581802602</v>
+        <v>0.1555783581802602</v>
       </c>
       <c r="C65">
-        <v>-937.7831081370693</v>
+        <v>-979.3430086379549</v>
       </c>
       <c r="D65">
-        <v>842.4308918629305</v>
+        <v>831.448991362045</v>
       </c>
       <c r="E65">
-        <v>1147.314</v>
+        <v>1177.892</v>
       </c>
       <c r="F65">
-        <v>1926.414</v>
+        <v>1956.992</v>
       </c>
       <c r="G65">
         <v>146.2</v>
@@ -6623,37 +6623,37 @@
         <v>211.3999999999999</v>
       </c>
       <c r="M65">
-        <v>386.8239311999999</v>
+        <v>392.9639936</v>
       </c>
       <c r="N65">
-        <v>-175.4239312</v>
+        <v>-181.5639936000001</v>
       </c>
       <c r="O65">
-        <v>-36.13732982720001</v>
+        <v>-37.40218268160002</v>
       </c>
       <c r="P65">
-        <v>-139.2866013728</v>
+        <v>-144.1618109184001</v>
       </c>
       <c r="Q65">
-        <v>142.3133986272</v>
+        <v>137.4381890816</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1128813529985342</v>
+        <v>0.1147447239151602</v>
       </c>
       <c r="T65">
-        <v>1.549222932991553</v>
+        <v>1.59225690335243</v>
       </c>
       <c r="U65">
         <v>0.2008</v>
       </c>
       <c r="V65">
-        <v>0.1125793842818999</v>
+        <v>0.1108203314024952</v>
       </c>
       <c r="W65">
-        <v>0.1781940596361945</v>
+        <v>0.178547277454379</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.5465018654461158</v>
+        <v>0.5379627737985202</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6669,22 +6669,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1555783581802602</v>
+        <v>0.1571283581802602</v>
       </c>
       <c r="C66">
-        <v>-979.3430086379549</v>
+        <v>-1020.62027419432</v>
       </c>
       <c r="D66">
-        <v>831.448991362045</v>
+        <v>820.7497258056803</v>
       </c>
       <c r="E66">
-        <v>1177.892</v>
+        <v>1208.47</v>
       </c>
       <c r="F66">
-        <v>1956.992</v>
+        <v>1987.57</v>
       </c>
       <c r="G66">
         <v>146.2</v>
@@ -6705,37 +6705,37 @@
         <v>211.3999999999999</v>
       </c>
       <c r="M66">
-        <v>392.9639936</v>
+        <v>399.104056</v>
       </c>
       <c r="N66">
-        <v>-181.5639936000001</v>
+        <v>-187.7040560000001</v>
       </c>
       <c r="O66">
-        <v>-37.40218268160002</v>
+        <v>-38.66703553600002</v>
       </c>
       <c r="P66">
-        <v>-144.1618109184001</v>
+        <v>-149.0370204640001</v>
       </c>
       <c r="Q66">
-        <v>137.4381890816</v>
+        <v>132.5629795359999</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1147447239151602</v>
+        <v>0.1167145731698791</v>
       </c>
       <c r="T66">
-        <v>1.59225690335243</v>
+        <v>1.637749957733928</v>
       </c>
       <c r="U66">
         <v>0.2008</v>
       </c>
       <c r="V66">
-        <v>0.1108203314024952</v>
+        <v>0.1091154032270722</v>
       </c>
       <c r="W66">
-        <v>0.178547277454379</v>
+        <v>0.1788896270320039</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.5379627737985202</v>
+        <v>0.529686423432389</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6751,22 +6751,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1571283581802602</v>
+        <v>0.1586783581802602</v>
       </c>
       <c r="C67">
-        <v>-1020.62027419432</v>
+        <v>-1061.625677207468</v>
       </c>
       <c r="D67">
-        <v>820.7497258056803</v>
+        <v>810.3223227925321</v>
       </c>
       <c r="E67">
-        <v>1208.47</v>
+        <v>1239.048</v>
       </c>
       <c r="F67">
-        <v>1987.57</v>
+        <v>2018.148</v>
       </c>
       <c r="G67">
         <v>146.2</v>
@@ -6787,37 +6787,37 @@
         <v>211.3999999999999</v>
       </c>
       <c r="M67">
-        <v>399.104056</v>
+        <v>405.2441184</v>
       </c>
       <c r="N67">
-        <v>-187.7040560000001</v>
+        <v>-193.8441184000001</v>
       </c>
       <c r="O67">
-        <v>-38.66703553600002</v>
+        <v>-39.93188839040002</v>
       </c>
       <c r="P67">
-        <v>-149.0370204640001</v>
+        <v>-153.9122300096001</v>
       </c>
       <c r="Q67">
-        <v>132.5629795359999</v>
+        <v>127.6877699904</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1167145731698791</v>
+        <v>0.1188002959101696</v>
       </c>
       <c r="T67">
-        <v>1.637749957733928</v>
+        <v>1.685919074137867</v>
       </c>
       <c r="U67">
         <v>0.2008</v>
       </c>
       <c r="V67">
-        <v>0.1091154032270722</v>
+        <v>0.1074621395418135</v>
       </c>
       <c r="W67">
-        <v>0.1788896270320039</v>
+        <v>0.1792216023800039</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.529686423432389</v>
+        <v>0.5216608715622013</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6833,22 +6833,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1586783581802602</v>
+        <v>0.1602283581802602</v>
       </c>
       <c r="C68">
-        <v>-1061.625677207468</v>
+        <v>-1102.369449504783</v>
       </c>
       <c r="D68">
-        <v>810.3223227925321</v>
+        <v>800.1565504952169</v>
       </c>
       <c r="E68">
-        <v>1239.048</v>
+        <v>1269.626</v>
       </c>
       <c r="F68">
-        <v>2018.148</v>
+        <v>2048.726</v>
       </c>
       <c r="G68">
         <v>146.2</v>
@@ -6869,37 +6869,37 @@
         <v>211.3999999999999</v>
       </c>
       <c r="M68">
-        <v>405.2441184</v>
+        <v>411.3841808</v>
       </c>
       <c r="N68">
-        <v>-193.8441184000001</v>
+        <v>-199.9841808000001</v>
       </c>
       <c r="O68">
-        <v>-39.93188839040002</v>
+        <v>-41.19674124480002</v>
       </c>
       <c r="P68">
-        <v>-153.9122300096001</v>
+        <v>-158.7874395552001</v>
       </c>
       <c r="Q68">
-        <v>127.6877699904</v>
+        <v>122.8125604447999</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1188002959101696</v>
+        <v>0.1210124260892657</v>
       </c>
       <c r="T68">
-        <v>1.685919074137867</v>
+        <v>1.737007530929924</v>
       </c>
       <c r="U68">
         <v>0.2008</v>
       </c>
       <c r="V68">
-        <v>0.1074621395418135</v>
+        <v>0.1058582270113387</v>
       </c>
       <c r="W68">
-        <v>0.1792216023800039</v>
+        <v>0.1795436680161232</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.5216608715622013</v>
+        <v>0.5138748884045565</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6915,22 +6915,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1602283581802602</v>
+        <v>0.1617783581802602</v>
       </c>
       <c r="C69">
-        <v>-1102.369449504783</v>
+        <v>-1142.861315828034</v>
       </c>
       <c r="D69">
-        <v>800.1565504952169</v>
+        <v>790.2426841719665</v>
       </c>
       <c r="E69">
-        <v>1269.626</v>
+        <v>1300.204</v>
       </c>
       <c r="F69">
-        <v>2048.726</v>
+        <v>2079.304</v>
       </c>
       <c r="G69">
         <v>146.2</v>
@@ -6951,37 +6951,37 @@
         <v>211.3999999999999</v>
       </c>
       <c r="M69">
-        <v>411.3841808</v>
+        <v>417.5242432000001</v>
       </c>
       <c r="N69">
-        <v>-199.9841808000001</v>
+        <v>-206.1242432000001</v>
       </c>
       <c r="O69">
-        <v>-41.19674124480002</v>
+        <v>-42.46159409920003</v>
       </c>
       <c r="P69">
-        <v>-158.7874395552001</v>
+        <v>-163.6626491008001</v>
       </c>
       <c r="Q69">
-        <v>122.8125604447999</v>
+        <v>117.9373508991999</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1210124260892657</v>
+        <v>0.1233628144045552</v>
       </c>
       <c r="T69">
-        <v>1.737007530929924</v>
+        <v>1.791289016271484</v>
       </c>
       <c r="U69">
         <v>0.2008</v>
       </c>
       <c r="V69">
-        <v>0.1058582270113387</v>
+        <v>0.1043014883788189</v>
       </c>
       <c r="W69">
-        <v>0.1795436680161232</v>
+        <v>0.1798562611335332</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.5138748884045565</v>
+        <v>0.5063179047515483</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6997,22 +6997,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1617783581802602</v>
+        <v>0.1877595977542183</v>
       </c>
       <c r="C70">
-        <v>-1142.861315828034</v>
+        <v>-1309.33466687171</v>
       </c>
       <c r="D70">
-        <v>790.2426841719665</v>
+        <v>654.3473331282904</v>
       </c>
       <c r="E70">
-        <v>1300.204</v>
+        <v>1330.782</v>
       </c>
       <c r="F70">
-        <v>2079.304</v>
+        <v>2109.882</v>
       </c>
       <c r="G70">
         <v>146.2</v>
@@ -7033,45 +7033,45 @@
         <v>211.3999999999999</v>
       </c>
       <c r="M70">
-        <v>417.5242432000001</v>
+        <v>497.5101756</v>
       </c>
       <c r="N70">
-        <v>-206.1242432000001</v>
+        <v>-286.1101756000001</v>
       </c>
       <c r="O70">
-        <v>-42.46159409920003</v>
+        <v>-58.93869617360003</v>
       </c>
       <c r="P70">
-        <v>-163.6626491008001</v>
+        <v>-227.1714794264001</v>
       </c>
       <c r="Q70">
-        <v>117.9373508991999</v>
+        <v>54.42852057359994</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1233628144045552</v>
+        <v>0.1267720651077928</v>
       </c>
       <c r="T70">
-        <v>1.791289016271484</v>
+        <v>1.870024598332398</v>
       </c>
       <c r="U70">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.1043014883788189</v>
+        <v>0.08753268201495652</v>
       </c>
       <c r="W70">
-        <v>0.1798562611335332</v>
+        <v>0.2151597935808733</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y70">
-        <v>0.5063179047515483</v>
+        <v>0.4249159321114394</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7079,22 +7079,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1877595977542183</v>
+        <v>0.1896595977542183</v>
       </c>
       <c r="C71">
-        <v>-1309.33466687171</v>
+        <v>-1348.039448956831</v>
       </c>
       <c r="D71">
-        <v>654.3473331282904</v>
+        <v>646.2205510431692</v>
       </c>
       <c r="E71">
-        <v>1330.782</v>
+        <v>1361.36</v>
       </c>
       <c r="F71">
-        <v>2109.882</v>
+        <v>2140.46</v>
       </c>
       <c r="G71">
         <v>146.2</v>
@@ -7115,37 +7115,37 @@
         <v>211.3999999999999</v>
       </c>
       <c r="M71">
-        <v>497.5101756</v>
+        <v>504.720468</v>
       </c>
       <c r="N71">
-        <v>-286.1101756000001</v>
+        <v>-293.3204680000001</v>
       </c>
       <c r="O71">
-        <v>-58.93869617360003</v>
+        <v>-60.42401640800003</v>
       </c>
       <c r="P71">
-        <v>-227.1714794264001</v>
+        <v>-232.8964515920001</v>
       </c>
       <c r="Q71">
-        <v>54.42852057359994</v>
+        <v>48.70354840799993</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1267720651077928</v>
+        <v>0.1294711339447193</v>
       </c>
       <c r="T71">
-        <v>1.870024598332398</v>
+        <v>1.932358751610145</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.08753268201495652</v>
+        <v>0.08628221512902857</v>
       </c>
       <c r="W71">
-        <v>0.2151597935808733</v>
+        <v>0.2154546536725751</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.4249159321114394</v>
+        <v>0.4188457045098474</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7161,22 +7161,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1896595977542183</v>
+        <v>0.1915595977542183</v>
       </c>
       <c r="C72">
-        <v>-1348.039448956831</v>
+        <v>-1386.54484336614</v>
       </c>
       <c r="D72">
-        <v>646.2205510431692</v>
+        <v>638.2931566338606</v>
       </c>
       <c r="E72">
-        <v>1361.36</v>
+        <v>1391.938</v>
       </c>
       <c r="F72">
-        <v>2140.46</v>
+        <v>2171.038</v>
       </c>
       <c r="G72">
         <v>146.2</v>
@@ -7197,37 +7197,37 @@
         <v>211.3999999999999</v>
       </c>
       <c r="M72">
-        <v>504.720468</v>
+        <v>511.9307604</v>
       </c>
       <c r="N72">
-        <v>-293.3204680000001</v>
+        <v>-300.5307604000001</v>
       </c>
       <c r="O72">
-        <v>-60.42401640800003</v>
+        <v>-61.90933664240002</v>
       </c>
       <c r="P72">
-        <v>-232.8964515920001</v>
+        <v>-238.6214237576</v>
       </c>
       <c r="Q72">
-        <v>48.70354840799993</v>
+        <v>42.97857624239998</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1294711339447193</v>
+        <v>0.1323563454600545</v>
       </c>
       <c r="T72">
-        <v>1.932358751610145</v>
+        <v>1.998991812010495</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.08628221512902857</v>
+        <v>0.08506697266242255</v>
       </c>
       <c r="W72">
-        <v>0.2154546536725751</v>
+        <v>0.2157412078462008</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.4188457045098474</v>
+        <v>0.4129464692350608</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7243,22 +7243,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1915595977542183</v>
+        <v>0.1934595977542183</v>
       </c>
       <c r="C73">
-        <v>-1386.544843366139</v>
+        <v>-1424.858099032041</v>
       </c>
       <c r="D73">
-        <v>638.2931566338606</v>
+        <v>630.5579009679589</v>
       </c>
       <c r="E73">
-        <v>1391.938</v>
+        <v>1422.516</v>
       </c>
       <c r="F73">
-        <v>2171.038</v>
+        <v>2201.616</v>
       </c>
       <c r="G73">
         <v>146.2</v>
@@ -7279,37 +7279,37 @@
         <v>211.3999999999999</v>
       </c>
       <c r="M73">
-        <v>511.9307603999999</v>
+        <v>519.1410527999999</v>
       </c>
       <c r="N73">
-        <v>-300.5307604</v>
+        <v>-307.7410528</v>
       </c>
       <c r="O73">
-        <v>-61.90933664240001</v>
+        <v>-63.3946568768</v>
       </c>
       <c r="P73">
-        <v>-238.6214237576</v>
+        <v>-244.3463959232</v>
       </c>
       <c r="Q73">
-        <v>42.97857624240001</v>
+        <v>37.25360407680006</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1323563454600544</v>
+        <v>0.1354476435121992</v>
       </c>
       <c r="T73">
-        <v>1.998991812010494</v>
+        <v>2.070384376725155</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.08506697266242255</v>
+        <v>0.08388548693100004</v>
       </c>
       <c r="W73">
-        <v>0.2157412078462008</v>
+        <v>0.2160198021816702</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.412946469235061</v>
+        <v>0.4072111016067962</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7325,22 +7325,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1934595977542183</v>
+        <v>0.1953595977542183</v>
       </c>
       <c r="C74">
-        <v>-1424.858099032041</v>
+        <v>-1462.986117705026</v>
       </c>
       <c r="D74">
-        <v>630.5579009679589</v>
+        <v>623.0078822949744</v>
       </c>
       <c r="E74">
-        <v>1422.516</v>
+        <v>1453.094</v>
       </c>
       <c r="F74">
-        <v>2201.616</v>
+        <v>2232.194</v>
       </c>
       <c r="G74">
         <v>146.2</v>
@@ -7361,37 +7361,37 @@
         <v>211.3999999999999</v>
       </c>
       <c r="M74">
-        <v>519.1410527999999</v>
+        <v>526.3513452</v>
       </c>
       <c r="N74">
-        <v>-307.7410528</v>
+        <v>-314.9513452</v>
       </c>
       <c r="O74">
-        <v>-63.3946568768</v>
+        <v>-64.87997711120002</v>
       </c>
       <c r="P74">
-        <v>-244.3463959232</v>
+        <v>-250.0713680888</v>
       </c>
       <c r="Q74">
-        <v>37.25360407680006</v>
+        <v>31.52863191119999</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1354476435121992</v>
+        <v>0.1387679266052436</v>
       </c>
       <c r="T74">
-        <v>2.070384376725155</v>
+        <v>2.147065279566827</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.08388548693100004</v>
+        <v>0.08273637067167125</v>
       </c>
       <c r="W74">
-        <v>0.2160198021816702</v>
+        <v>0.2162907637956199</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.4072111016067962</v>
+        <v>0.4016328673382099</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7407,22 +7407,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1953595977542183</v>
+        <v>0.1972595977542183</v>
       </c>
       <c r="C75">
-        <v>-1462.986117705026</v>
+        <v>-1500.935474492747</v>
       </c>
       <c r="D75">
-        <v>623.0078822949744</v>
+        <v>615.6365255072534</v>
       </c>
       <c r="E75">
-        <v>1453.094</v>
+        <v>1483.672</v>
       </c>
       <c r="F75">
-        <v>2232.194</v>
+        <v>2262.772</v>
       </c>
       <c r="G75">
         <v>146.2</v>
@@ -7443,37 +7443,37 @@
         <v>211.3999999999999</v>
       </c>
       <c r="M75">
-        <v>526.3513452</v>
+        <v>533.5616376</v>
       </c>
       <c r="N75">
-        <v>-314.9513452</v>
+        <v>-322.1616376000001</v>
       </c>
       <c r="O75">
-        <v>-64.87997711120002</v>
+        <v>-66.36529734560003</v>
       </c>
       <c r="P75">
-        <v>-250.0713680888</v>
+        <v>-255.7963402544001</v>
       </c>
       <c r="Q75">
-        <v>31.52863191119999</v>
+        <v>25.80365974559993</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1387679266052436</v>
+        <v>0.1423436160900607</v>
       </c>
       <c r="T75">
-        <v>2.147065279566827</v>
+        <v>2.229644713396321</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.08273637067167125</v>
+        <v>0.08161831160854055</v>
       </c>
       <c r="W75">
-        <v>0.2162907637956199</v>
+        <v>0.2165544021227062</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.4016328673382099</v>
+        <v>0.3962053961579638</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7489,22 +7489,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1972595977542183</v>
+        <v>0.1991595977542183</v>
       </c>
       <c r="C76">
-        <v>-1500.935474492747</v>
+        <v>-1538.712436958055</v>
       </c>
       <c r="D76">
-        <v>615.6365255072534</v>
+        <v>608.4375630419446</v>
       </c>
       <c r="E76">
-        <v>1483.672</v>
+        <v>1514.25</v>
       </c>
       <c r="F76">
-        <v>2262.772</v>
+        <v>2293.35</v>
       </c>
       <c r="G76">
         <v>146.2</v>
@@ -7525,37 +7525,37 @@
         <v>211.3999999999999</v>
       </c>
       <c r="M76">
-        <v>533.5616376</v>
+        <v>540.77193</v>
       </c>
       <c r="N76">
-        <v>-322.1616376000001</v>
+        <v>-329.3719300000001</v>
       </c>
       <c r="O76">
-        <v>-66.36529734560003</v>
+        <v>-67.85061758000002</v>
       </c>
       <c r="P76">
-        <v>-255.7963402544001</v>
+        <v>-261.5213124200001</v>
       </c>
       <c r="Q76">
-        <v>25.80365974559993</v>
+        <v>20.07868757999995</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1423436160900607</v>
+        <v>0.1462053607336631</v>
       </c>
       <c r="T76">
-        <v>2.229644713396321</v>
+        <v>2.318830501932174</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.08161831160854055</v>
+        <v>0.08053006745376001</v>
       </c>
       <c r="W76">
-        <v>0.2165544021227062</v>
+        <v>0.2168110100944034</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.3962053961579638</v>
+        <v>0.3909226575425243</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7571,22 +7571,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1991595977542183</v>
+        <v>0.2010595977542183</v>
       </c>
       <c r="C77">
-        <v>-1538.712436958055</v>
+        <v>-1576.322982892586</v>
       </c>
       <c r="D77">
-        <v>608.4375630419446</v>
+        <v>601.4050171074134</v>
       </c>
       <c r="E77">
-        <v>1514.25</v>
+        <v>1544.828</v>
       </c>
       <c r="F77">
-        <v>2293.35</v>
+        <v>2323.928</v>
       </c>
       <c r="G77">
         <v>146.2</v>
@@ -7607,37 +7607,37 @@
         <v>211.3999999999999</v>
       </c>
       <c r="M77">
-        <v>540.77193</v>
+        <v>547.9822224</v>
       </c>
       <c r="N77">
-        <v>-329.3719300000001</v>
+        <v>-336.5822224</v>
       </c>
       <c r="O77">
-        <v>-67.85061758000002</v>
+        <v>-69.33593781440001</v>
       </c>
       <c r="P77">
-        <v>-261.5213124200001</v>
+        <v>-267.2462845856001</v>
       </c>
       <c r="Q77">
-        <v>20.07868757999995</v>
+        <v>14.35371541439997</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1462053607336631</v>
+        <v>0.1503889174308991</v>
       </c>
       <c r="T77">
-        <v>2.318830501932174</v>
+        <v>2.415448439512681</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.08053006745376001</v>
+        <v>0.07947046130305264</v>
       </c>
       <c r="W77">
-        <v>0.2168110100944034</v>
+        <v>0.2170608652247402</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.3909226575425243</v>
+        <v>0.3857789383643332</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7653,22 +7653,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2010595977542183</v>
+        <v>0.2029595977542183</v>
       </c>
       <c r="C78">
-        <v>-1576.322982892586</v>
+        <v>-1613.772816871818</v>
       </c>
       <c r="D78">
-        <v>601.4050171074134</v>
+        <v>594.5331831281821</v>
       </c>
       <c r="E78">
-        <v>1544.828</v>
+        <v>1575.406</v>
       </c>
       <c r="F78">
-        <v>2323.928</v>
+        <v>2354.506</v>
       </c>
       <c r="G78">
         <v>146.2</v>
@@ -7689,37 +7689,37 @@
         <v>211.3999999999999</v>
       </c>
       <c r="M78">
-        <v>547.9822224</v>
+        <v>555.1925148</v>
       </c>
       <c r="N78">
-        <v>-336.5822224</v>
+        <v>-343.7925148000001</v>
       </c>
       <c r="O78">
-        <v>-69.33593781440001</v>
+        <v>-70.82125804880003</v>
       </c>
       <c r="P78">
-        <v>-267.2462845856001</v>
+        <v>-272.9712567512001</v>
       </c>
       <c r="Q78">
-        <v>14.35371541439997</v>
+        <v>8.628743248799935</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1503889174308991</v>
+        <v>0.1549362616670251</v>
       </c>
       <c r="T78">
-        <v>2.415448439512681</v>
+        <v>2.520467936882797</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.07947046130305264</v>
+        <v>0.07843837739002597</v>
       </c>
       <c r="W78">
-        <v>0.2170608652247402</v>
+        <v>0.2173042306114319</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.3857789383643332</v>
+        <v>0.3807688222816795</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7735,22 +7735,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2029595977542183</v>
+        <v>0.2048595977542183</v>
       </c>
       <c r="C79">
-        <v>-1613.772816871818</v>
+        <v>-1651.067385687978</v>
       </c>
       <c r="D79">
-        <v>594.5331831281821</v>
+        <v>587.8166143120224</v>
       </c>
       <c r="E79">
-        <v>1575.406</v>
+        <v>1605.984</v>
       </c>
       <c r="F79">
-        <v>2354.506</v>
+        <v>2385.084</v>
       </c>
       <c r="G79">
         <v>146.2</v>
@@ -7771,37 +7771,37 @@
         <v>211.3999999999999</v>
       </c>
       <c r="M79">
-        <v>555.1925148</v>
+        <v>562.4028072</v>
       </c>
       <c r="N79">
-        <v>-343.7925148000001</v>
+        <v>-351.0028072000001</v>
       </c>
       <c r="O79">
-        <v>-70.82125804880003</v>
+        <v>-72.30657828320003</v>
       </c>
       <c r="P79">
-        <v>-272.9712567512001</v>
+        <v>-278.6962289168</v>
       </c>
       <c r="Q79">
-        <v>8.628743248799935</v>
+        <v>2.903771083200013</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1549362616670251</v>
+        <v>0.1598970008337081</v>
       </c>
       <c r="T79">
-        <v>2.520467936882797</v>
+        <v>2.635034661286561</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.07843837739002597</v>
+        <v>0.07743275716707693</v>
       </c>
       <c r="W79">
-        <v>0.2173042306114319</v>
+        <v>0.2175413558600033</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.3807688222816795</v>
+        <v>0.3758871707139657</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7817,22 +7817,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2048595977542183</v>
+        <v>0.2067595977542183</v>
       </c>
       <c r="C80">
-        <v>-1651.067385687978</v>
+        <v>-1688.211892748548</v>
       </c>
       <c r="D80">
-        <v>587.8166143120224</v>
+        <v>581.2501072514519</v>
       </c>
       <c r="E80">
-        <v>1605.984</v>
+        <v>1636.562</v>
       </c>
       <c r="F80">
-        <v>2385.084</v>
+        <v>2415.662</v>
       </c>
       <c r="G80">
         <v>146.2</v>
@@ -7853,37 +7853,37 @@
         <v>211.3999999999999</v>
       </c>
       <c r="M80">
-        <v>562.4028072</v>
+        <v>569.6130995999999</v>
       </c>
       <c r="N80">
-        <v>-351.0028072000001</v>
+        <v>-358.2130996</v>
       </c>
       <c r="O80">
-        <v>-72.30657828320003</v>
+        <v>-73.7918985176</v>
       </c>
       <c r="P80">
-        <v>-278.6962289168</v>
+        <v>-284.4212010824</v>
       </c>
       <c r="Q80">
-        <v>2.903771083200013</v>
+        <v>-2.821201082399966</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1598970008337081</v>
+        <v>0.165330191349599</v>
       </c>
       <c r="T80">
-        <v>2.635034661286561</v>
+        <v>2.760512502300208</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.07743275716707693</v>
+        <v>0.07645259568394938</v>
       </c>
       <c r="W80">
-        <v>0.2175413558600033</v>
+        <v>0.2177724779377248</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.3758871707139657</v>
+        <v>0.3711291052618902</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7899,22 +7899,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2067595977542183</v>
+        <v>0.2086595977542183</v>
       </c>
       <c r="C81">
-        <v>-1688.211892748548</v>
+        <v>-1725.211311520349</v>
       </c>
       <c r="D81">
-        <v>581.2501072514519</v>
+        <v>574.8286884796505</v>
       </c>
       <c r="E81">
-        <v>1636.562</v>
+        <v>1667.14</v>
       </c>
       <c r="F81">
-        <v>2415.662</v>
+        <v>2446.24</v>
       </c>
       <c r="G81">
         <v>146.2</v>
@@ -7935,37 +7935,37 @@
         <v>211.3999999999999</v>
       </c>
       <c r="M81">
-        <v>569.6130995999999</v>
+        <v>576.823392</v>
       </c>
       <c r="N81">
-        <v>-358.2130996</v>
+        <v>-365.4233920000001</v>
       </c>
       <c r="O81">
-        <v>-73.7918985176</v>
+        <v>-75.27721875200002</v>
       </c>
       <c r="P81">
-        <v>-284.4212010824</v>
+        <v>-290.1461732480001</v>
       </c>
       <c r="Q81">
-        <v>-2.821201082399966</v>
+        <v>-8.546173248000059</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.165330191349599</v>
+        <v>0.1713067009170789</v>
       </c>
       <c r="T81">
-        <v>2.760512502300208</v>
+        <v>2.898538127415218</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.07645259568394938</v>
+        <v>0.0754969382379</v>
       </c>
       <c r="W81">
-        <v>0.2177724779377248</v>
+        <v>0.2179978219635032</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.3711291052618902</v>
+        <v>0.3664899914461165</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7981,22 +7981,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2086595977542183</v>
+        <v>0.2105595977542183</v>
       </c>
       <c r="C82">
-        <v>-1725.211311520349</v>
+        <v>-1762.070398092217</v>
       </c>
       <c r="D82">
-        <v>574.8286884796505</v>
+        <v>568.547601907783</v>
       </c>
       <c r="E82">
-        <v>1667.14</v>
+        <v>1697.718</v>
       </c>
       <c r="F82">
-        <v>2446.24</v>
+        <v>2476.818</v>
       </c>
       <c r="G82">
         <v>146.2</v>
@@ -8017,37 +8017,37 @@
         <v>211.3999999999999</v>
       </c>
       <c r="M82">
-        <v>576.823392</v>
+        <v>584.0336844</v>
       </c>
       <c r="N82">
-        <v>-365.4233920000001</v>
+        <v>-372.6336844</v>
       </c>
       <c r="O82">
-        <v>-75.27721875200002</v>
+        <v>-76.76253898640002</v>
       </c>
       <c r="P82">
-        <v>-290.1461732480001</v>
+        <v>-295.8711454136001</v>
       </c>
       <c r="Q82">
-        <v>-8.546173248000059</v>
+        <v>-14.27114541360004</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1713067009170789</v>
+        <v>0.1779123167548199</v>
       </c>
       <c r="T82">
-        <v>2.898538127415218</v>
+        <v>3.05109276570023</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.0754969382379</v>
+        <v>0.07456487727200001</v>
       </c>
       <c r="W82">
-        <v>0.2179978219635032</v>
+        <v>0.2182176019392624</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.3664899914461165</v>
+        <v>0.3619654236504855</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8063,22 +8063,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2105595977542183</v>
+        <v>0.2124595977542184</v>
       </c>
       <c r="C83">
-        <v>-1762.070398092217</v>
+        <v>-1798.79370292295</v>
       </c>
       <c r="D83">
-        <v>568.547601907783</v>
+        <v>562.4022970770503</v>
       </c>
       <c r="E83">
-        <v>1697.718</v>
+        <v>1728.296</v>
       </c>
       <c r="F83">
-        <v>2476.818</v>
+        <v>2507.396</v>
       </c>
       <c r="G83">
         <v>146.2</v>
@@ -8099,37 +8099,37 @@
         <v>211.3999999999999</v>
       </c>
       <c r="M83">
-        <v>584.0336844</v>
+        <v>591.2439768</v>
       </c>
       <c r="N83">
-        <v>-372.6336844</v>
+        <v>-379.8439768000001</v>
       </c>
       <c r="O83">
-        <v>-76.76253898640002</v>
+        <v>-78.24785922080004</v>
       </c>
       <c r="P83">
-        <v>-295.8711454136001</v>
+        <v>-301.5961175792001</v>
       </c>
       <c r="Q83">
-        <v>-14.27114541360004</v>
+        <v>-19.99611757920007</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.1779123167548199</v>
+        <v>0.1852518899078655</v>
       </c>
       <c r="T83">
-        <v>3.05109276570023</v>
+        <v>3.220597919350242</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.07456487727200001</v>
+        <v>0.07365554950039026</v>
       </c>
       <c r="W83">
-        <v>0.2182176019392624</v>
+        <v>0.218432021427808</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3619654236504855</v>
+        <v>0.3575512111669429</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8145,22 +8145,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2124595977542184</v>
+        <v>0.2143595977542183</v>
       </c>
       <c r="C84">
-        <v>-1798.79370292295</v>
+        <v>-1835.385581835528</v>
       </c>
       <c r="D84">
-        <v>562.4022970770503</v>
+        <v>556.3884181644722</v>
       </c>
       <c r="E84">
-        <v>1728.296</v>
+        <v>1758.874</v>
       </c>
       <c r="F84">
-        <v>2507.396</v>
+        <v>2537.974</v>
       </c>
       <c r="G84">
         <v>146.2</v>
@@ -8181,37 +8181,37 @@
         <v>211.3999999999999</v>
       </c>
       <c r="M84">
-        <v>591.2439768</v>
+        <v>598.4542692000001</v>
       </c>
       <c r="N84">
-        <v>-379.8439768000001</v>
+        <v>-387.0542692000002</v>
       </c>
       <c r="O84">
-        <v>-78.24785922080004</v>
+        <v>-79.73317945520004</v>
       </c>
       <c r="P84">
-        <v>-301.5961175792001</v>
+        <v>-307.3210897448001</v>
       </c>
       <c r="Q84">
-        <v>-19.99611757920007</v>
+        <v>-25.72108974480011</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.1852518899078655</v>
+        <v>0.193454942255387</v>
       </c>
       <c r="T84">
-        <v>3.220597919350242</v>
+        <v>3.41004485578261</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.07365554950039026</v>
+        <v>0.0727681332413494</v>
       </c>
       <c r="W84">
-        <v>0.218432021427808</v>
+        <v>0.2186412741816898</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3575512111669429</v>
+        <v>0.3532433652492689</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8227,22 +8227,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2143595977542183</v>
+        <v>0.2162595977542184</v>
       </c>
       <c r="C85">
-        <v>-1835.385581835528</v>
+        <v>-1871.850206313406</v>
       </c>
       <c r="D85">
-        <v>556.3884181644722</v>
+        <v>550.5017936865945</v>
       </c>
       <c r="E85">
-        <v>1758.874</v>
+        <v>1789.452</v>
       </c>
       <c r="F85">
-        <v>2537.974</v>
+        <v>2568.552</v>
       </c>
       <c r="G85">
         <v>146.2</v>
@@ -8263,37 +8263,37 @@
         <v>211.3999999999999</v>
       </c>
       <c r="M85">
-        <v>598.4542692000001</v>
+        <v>605.6645616000001</v>
       </c>
       <c r="N85">
-        <v>-387.0542692000002</v>
+        <v>-394.2645616000001</v>
       </c>
       <c r="O85">
-        <v>-79.73317945520004</v>
+        <v>-81.21849968960004</v>
       </c>
       <c r="P85">
-        <v>-307.3210897448001</v>
+        <v>-313.0460619104001</v>
       </c>
       <c r="Q85">
-        <v>-25.72108974480011</v>
+        <v>-31.44606191040009</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.193454942255387</v>
+        <v>0.2026833761463487</v>
       </c>
       <c r="T85">
-        <v>3.41004485578261</v>
+        <v>3.623172659269024</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.0727681332413494</v>
+        <v>0.07190184594085715</v>
       </c>
       <c r="W85">
-        <v>0.2186412741816898</v>
+        <v>0.2188455447271459</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3532433652492689</v>
+        <v>0.3490380870915395</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8309,22 +8309,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2162595977542183</v>
+        <v>0.2181595977542183</v>
       </c>
       <c r="C86">
-        <v>-1871.850206313405</v>
+        <v>-1908.191573150037</v>
       </c>
       <c r="D86">
-        <v>550.5017936865951</v>
+        <v>544.7384268499626</v>
       </c>
       <c r="E86">
-        <v>1789.452</v>
+        <v>1820.03</v>
       </c>
       <c r="F86">
-        <v>2568.552</v>
+        <v>2599.13</v>
       </c>
       <c r="G86">
         <v>146.2</v>
@@ -8345,37 +8345,37 @@
         <v>211.3999999999999</v>
       </c>
       <c r="M86">
-        <v>605.6645616</v>
+        <v>612.8748539999999</v>
       </c>
       <c r="N86">
-        <v>-394.2645616</v>
+        <v>-401.474854</v>
       </c>
       <c r="O86">
-        <v>-81.21849968960001</v>
+        <v>-82.703819924</v>
       </c>
       <c r="P86">
-        <v>-313.0460619104</v>
+        <v>-318.771034076</v>
       </c>
       <c r="Q86">
-        <v>-31.44606191039998</v>
+        <v>-37.17103407599996</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2026833761463486</v>
+        <v>0.2131422678894385</v>
       </c>
       <c r="T86">
-        <v>3.623172659269021</v>
+        <v>3.864717503220289</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.07190184594085715</v>
+        <v>0.07105594187096473</v>
       </c>
       <c r="W86">
-        <v>0.2188455447271459</v>
+        <v>0.2190450089068265</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3490380870915396</v>
+        <v>0.3449317566551685</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8391,22 +8391,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2181595977542183</v>
+        <v>0.2200595977542183</v>
       </c>
       <c r="C87">
-        <v>-1908.191573150037</v>
+        <v>-1944.413513498545</v>
       </c>
       <c r="D87">
-        <v>544.7384268499626</v>
+        <v>539.0944865014545</v>
       </c>
       <c r="E87">
-        <v>1820.03</v>
+        <v>1850.608</v>
       </c>
       <c r="F87">
-        <v>2599.13</v>
+        <v>2629.708</v>
       </c>
       <c r="G87">
         <v>146.2</v>
@@ -8427,37 +8427,37 @@
         <v>211.3999999999999</v>
       </c>
       <c r="M87">
-        <v>612.8748539999999</v>
+        <v>620.0851464</v>
       </c>
       <c r="N87">
-        <v>-401.474854</v>
+        <v>-408.6851464000001</v>
       </c>
       <c r="O87">
-        <v>-82.703819924</v>
+        <v>-84.18914015840002</v>
       </c>
       <c r="P87">
-        <v>-318.771034076</v>
+        <v>-324.4960062416001</v>
       </c>
       <c r="Q87">
-        <v>-37.17103407599996</v>
+        <v>-42.89600624160005</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2131422678894385</v>
+        <v>0.2250952870243984</v>
       </c>
       <c r="T87">
-        <v>3.864717503220289</v>
+        <v>4.14076875345031</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.07105594187096473</v>
+        <v>0.0702297099887442</v>
       </c>
       <c r="W87">
-        <v>0.2190450089068265</v>
+        <v>0.2192398343846541</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3449317566551685</v>
+        <v>0.3409209222754572</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8473,22 +8473,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2200595977542183</v>
+        <v>0.2219595977542184</v>
       </c>
       <c r="C88">
-        <v>-1944.413513498545</v>
+        <v>-1980.519701364575</v>
       </c>
       <c r="D88">
-        <v>539.0944865014545</v>
+        <v>533.5662986354243</v>
       </c>
       <c r="E88">
-        <v>1850.608</v>
+        <v>1881.186</v>
       </c>
       <c r="F88">
-        <v>2629.708</v>
+        <v>2660.286</v>
       </c>
       <c r="G88">
         <v>146.2</v>
@@ -8509,37 +8509,37 @@
         <v>211.3999999999999</v>
       </c>
       <c r="M88">
-        <v>620.0851464</v>
+        <v>627.2954387999999</v>
       </c>
       <c r="N88">
-        <v>-408.6851464000001</v>
+        <v>-415.8954388</v>
       </c>
       <c r="O88">
-        <v>-84.18914015840002</v>
+        <v>-85.67446039280001</v>
       </c>
       <c r="P88">
-        <v>-324.4960062416001</v>
+        <v>-330.2209784072</v>
       </c>
       <c r="Q88">
-        <v>-42.89600624160005</v>
+        <v>-48.62097840719997</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2250952870243984</v>
+        <v>0.2388872321801214</v>
       </c>
       <c r="T88">
-        <v>4.14076875345031</v>
+        <v>4.459289426792642</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.0702297099887442</v>
+        <v>0.06942247194289657</v>
       </c>
       <c r="W88">
-        <v>0.2192398343846541</v>
+        <v>0.219430181115865</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3409209222754572</v>
+        <v>0.3370022909849347</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8555,22 +8555,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2219595977542184</v>
+        <v>0.2238595977542183</v>
       </c>
       <c r="C89">
-        <v>-1980.519701364575</v>
+        <v>-2016.513661581922</v>
       </c>
       <c r="D89">
-        <v>533.5662986354243</v>
+        <v>528.1503384180774</v>
       </c>
       <c r="E89">
-        <v>1881.186</v>
+        <v>1911.764</v>
       </c>
       <c r="F89">
-        <v>2660.286</v>
+        <v>2690.864</v>
       </c>
       <c r="G89">
         <v>146.2</v>
@@ -8591,37 +8591,37 @@
         <v>211.3999999999999</v>
       </c>
       <c r="M89">
-        <v>627.2954387999999</v>
+        <v>634.5057311999999</v>
       </c>
       <c r="N89">
-        <v>-415.8954388</v>
+        <v>-423.1057312</v>
       </c>
       <c r="O89">
-        <v>-85.67446039280001</v>
+        <v>-87.15978062720001</v>
       </c>
       <c r="P89">
-        <v>-330.2209784072</v>
+        <v>-335.9459505728</v>
       </c>
       <c r="Q89">
-        <v>-48.62097840719997</v>
+        <v>-54.34595057279995</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2388872321801214</v>
+        <v>0.2549778348617981</v>
       </c>
       <c r="T89">
-        <v>4.459289426792642</v>
+        <v>4.830896879025362</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.06942247194289657</v>
+        <v>0.06863358021627275</v>
       </c>
       <c r="W89">
-        <v>0.219430181115865</v>
+        <v>0.2196162017850029</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3370022909849347</v>
+        <v>0.3331727194964696</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8637,22 +8637,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2238595977542183</v>
+        <v>0.2257595977542183</v>
       </c>
       <c r="C90">
-        <v>-2016.513661581922</v>
+        <v>-2052.398777307288</v>
       </c>
       <c r="D90">
-        <v>528.1503384180774</v>
+        <v>522.8432226927122</v>
       </c>
       <c r="E90">
-        <v>1911.764</v>
+        <v>1942.342</v>
       </c>
       <c r="F90">
-        <v>2690.864</v>
+        <v>2721.442</v>
       </c>
       <c r="G90">
         <v>146.2</v>
@@ -8673,37 +8673,37 @@
         <v>211.3999999999999</v>
       </c>
       <c r="M90">
-        <v>634.5057311999999</v>
+        <v>641.7160236</v>
       </c>
       <c r="N90">
-        <v>-423.1057312</v>
+        <v>-430.3160236000001</v>
       </c>
       <c r="O90">
-        <v>-87.15978062720001</v>
+        <v>-88.64510086160001</v>
       </c>
       <c r="P90">
-        <v>-335.9459505728</v>
+        <v>-341.6709227384</v>
       </c>
       <c r="Q90">
-        <v>-54.34595057279995</v>
+        <v>-60.07092273839999</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2549778348617981</v>
+        <v>0.2739940016674162</v>
       </c>
       <c r="T90">
-        <v>4.830896879025362</v>
+        <v>5.270069322573122</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.06863358021627275</v>
+        <v>0.06786241639361799</v>
       </c>
       <c r="W90">
-        <v>0.2196162017850029</v>
+        <v>0.2197980422143849</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3331727194964696</v>
+        <v>0.329429205794262</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8719,22 +8719,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2257595977542183</v>
+        <v>0.2276595977542183</v>
       </c>
       <c r="C91">
-        <v>-2052.398777307288</v>
+        <v>-2088.178297067675</v>
       </c>
       <c r="D91">
-        <v>522.8432226927122</v>
+        <v>517.6417029323247</v>
       </c>
       <c r="E91">
-        <v>1942.342</v>
+        <v>1972.92</v>
       </c>
       <c r="F91">
-        <v>2721.442</v>
+        <v>2752.02</v>
       </c>
       <c r="G91">
         <v>146.2</v>
@@ -8755,37 +8755,37 @@
         <v>211.3999999999999</v>
       </c>
       <c r="M91">
-        <v>641.7160236</v>
+        <v>648.926316</v>
       </c>
       <c r="N91">
-        <v>-430.3160236000001</v>
+        <v>-437.5263160000001</v>
       </c>
       <c r="O91">
-        <v>-88.64510086160001</v>
+        <v>-90.13042109600003</v>
       </c>
       <c r="P91">
-        <v>-341.6709227384</v>
+        <v>-347.3958949040001</v>
       </c>
       <c r="Q91">
-        <v>-60.07092273839999</v>
+        <v>-65.79589490400008</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.2739940016674162</v>
+        <v>0.2968134018341578</v>
       </c>
       <c r="T91">
-        <v>5.270069322573122</v>
+        <v>5.797076254830436</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.06786241639361799</v>
+        <v>0.0671083895448</v>
       </c>
       <c r="W91">
-        <v>0.2197980422143849</v>
+        <v>0.2199758417453362</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.329429205794262</v>
+        <v>0.3257688812854369</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8801,22 +8801,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2276595977542183</v>
+        <v>0.2295595977542183</v>
       </c>
       <c r="C92">
-        <v>-2088.178297067675</v>
+        <v>-2123.855341391258</v>
       </c>
       <c r="D92">
-        <v>517.6417029323247</v>
+        <v>512.542658608742</v>
       </c>
       <c r="E92">
-        <v>1972.92</v>
+        <v>2003.498</v>
       </c>
       <c r="F92">
-        <v>2752.02</v>
+        <v>2782.598</v>
       </c>
       <c r="G92">
         <v>146.2</v>
@@ -8837,37 +8837,37 @@
         <v>211.3999999999999</v>
       </c>
       <c r="M92">
-        <v>648.926316</v>
+        <v>656.1366084</v>
       </c>
       <c r="N92">
-        <v>-437.5263160000001</v>
+        <v>-444.7366084000001</v>
       </c>
       <c r="O92">
-        <v>-90.13042109600003</v>
+        <v>-91.61574133040003</v>
       </c>
       <c r="P92">
-        <v>-347.3958949040001</v>
+        <v>-353.1208670696001</v>
       </c>
       <c r="Q92">
-        <v>-65.79589490400008</v>
+        <v>-71.52086706960006</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.2968134018341578</v>
+        <v>0.324703779815731</v>
       </c>
       <c r="T92">
-        <v>5.797076254830436</v>
+        <v>6.441195838700484</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.0671083895448</v>
+        <v>0.06637093471463737</v>
       </c>
       <c r="W92">
-        <v>0.2199758417453362</v>
+        <v>0.2201497335942885</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3257688812854369</v>
+        <v>0.3221890034691134</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8883,22 +8883,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2295595977542183</v>
+        <v>0.2314595977542183</v>
       </c>
       <c r="C93">
-        <v>-2123.855341391258</v>
+        <v>-2159.432909050163</v>
       </c>
       <c r="D93">
-        <v>512.542658608742</v>
+        <v>507.5430909498367</v>
       </c>
       <c r="E93">
-        <v>2003.498</v>
+        <v>2034.076</v>
       </c>
       <c r="F93">
-        <v>2782.598</v>
+        <v>2813.176</v>
       </c>
       <c r="G93">
         <v>146.2</v>
@@ -8919,37 +8919,37 @@
         <v>211.3999999999999</v>
       </c>
       <c r="M93">
-        <v>656.1366084</v>
+        <v>663.3469008</v>
       </c>
       <c r="N93">
-        <v>-444.7366084000001</v>
+        <v>-451.9469008</v>
       </c>
       <c r="O93">
-        <v>-91.61574133040003</v>
+        <v>-93.10106156480002</v>
       </c>
       <c r="P93">
-        <v>-353.1208670696001</v>
+        <v>-358.8458392352</v>
       </c>
       <c r="Q93">
-        <v>-71.52086706960006</v>
+        <v>-77.24583923519998</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.324703779815731</v>
+        <v>0.3595667522926975</v>
       </c>
       <c r="T93">
-        <v>6.441195838700484</v>
+        <v>7.246345318538047</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.06637093471463737</v>
+        <v>0.0656495115112174</v>
       </c>
       <c r="W93">
-        <v>0.2201497335942885</v>
+        <v>0.2203198451856549</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3221890034691134</v>
+        <v>0.3186869490835796</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8965,22 +8965,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2314595977542183</v>
+        <v>0.2333595977542184</v>
       </c>
       <c r="C94">
-        <v>-2159.432909050163</v>
+        <v>-2194.913882941422</v>
       </c>
       <c r="D94">
-        <v>507.5430909498367</v>
+        <v>502.6401170585781</v>
       </c>
       <c r="E94">
-        <v>2034.076</v>
+        <v>2064.654</v>
       </c>
       <c r="F94">
-        <v>2813.176</v>
+        <v>2843.754</v>
       </c>
       <c r="G94">
         <v>146.2</v>
@@ -9001,37 +9001,37 @@
         <v>211.3999999999999</v>
       </c>
       <c r="M94">
-        <v>663.3469008</v>
+        <v>670.5571932</v>
       </c>
       <c r="N94">
-        <v>-451.9469008</v>
+        <v>-459.1571932000001</v>
       </c>
       <c r="O94">
-        <v>-93.10106156480002</v>
+        <v>-94.58638179920003</v>
       </c>
       <c r="P94">
-        <v>-358.8458392352</v>
+        <v>-364.5708114008001</v>
       </c>
       <c r="Q94">
-        <v>-77.24583923519998</v>
+        <v>-82.97081140080007</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.3595667522926975</v>
+        <v>0.4043905740487971</v>
       </c>
       <c r="T94">
-        <v>7.246345318538047</v>
+        <v>8.281537506900627</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.0656495115112174</v>
+        <v>0.06494360278529034</v>
       </c>
       <c r="W94">
-        <v>0.2203198451856549</v>
+        <v>0.2204862984632286</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3186869490835796</v>
+        <v>0.315260207695584</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9047,22 +9047,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2333595977542184</v>
+        <v>0.2352595977542184</v>
       </c>
       <c r="C95">
-        <v>-2194.913882941422</v>
+        <v>-2230.301035630303</v>
       </c>
       <c r="D95">
-        <v>502.6401170585781</v>
+        <v>497.8309643696972</v>
       </c>
       <c r="E95">
-        <v>2064.654</v>
+        <v>2095.232</v>
       </c>
       <c r="F95">
-        <v>2843.754</v>
+        <v>2874.332</v>
       </c>
       <c r="G95">
         <v>146.2</v>
@@ -9083,37 +9083,37 @@
         <v>211.3999999999999</v>
       </c>
       <c r="M95">
-        <v>670.5571932</v>
+        <v>677.7674856</v>
       </c>
       <c r="N95">
-        <v>-459.1571932000001</v>
+        <v>-466.3674856000001</v>
       </c>
       <c r="O95">
-        <v>-94.58638179920003</v>
+        <v>-96.07170203360002</v>
       </c>
       <c r="P95">
-        <v>-364.5708114008001</v>
+        <v>-370.2957835664</v>
       </c>
       <c r="Q95">
-        <v>-82.97081140080007</v>
+        <v>-88.6957835664</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.4043905740487971</v>
+        <v>0.4641556697235967</v>
       </c>
       <c r="T95">
-        <v>8.281537506900627</v>
+        <v>9.661793758050733</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.06494360278529034</v>
+        <v>0.06425271339395745</v>
       </c>
       <c r="W95">
-        <v>0.2204862984632286</v>
+        <v>0.2206492101817049</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.315260207695584</v>
+        <v>0.3119063756988226</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9129,22 +9129,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2352595977542184</v>
+        <v>0.2371595977542184</v>
       </c>
       <c r="C96">
-        <v>-2230.301035630303</v>
+        <v>-2265.59703457845</v>
       </c>
       <c r="D96">
-        <v>497.8309643696972</v>
+        <v>493.1129654215497</v>
       </c>
       <c r="E96">
-        <v>2095.232</v>
+        <v>2125.81</v>
       </c>
       <c r="F96">
-        <v>2874.332</v>
+        <v>2904.91</v>
       </c>
       <c r="G96">
         <v>146.2</v>
@@ -9165,37 +9165,37 @@
         <v>211.3999999999999</v>
       </c>
       <c r="M96">
-        <v>677.7674856</v>
+        <v>684.9777779999999</v>
       </c>
       <c r="N96">
-        <v>-466.3674856000001</v>
+        <v>-473.577778</v>
       </c>
       <c r="O96">
-        <v>-96.07170203360002</v>
+        <v>-97.55702226800001</v>
       </c>
       <c r="P96">
-        <v>-370.2957835664</v>
+        <v>-376.020755732</v>
       </c>
       <c r="Q96">
-        <v>-88.6957835664</v>
+        <v>-94.42075573199998</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.4641556697235967</v>
+        <v>0.5478268036683164</v>
       </c>
       <c r="T96">
-        <v>9.661793758050733</v>
+        <v>11.59415250966089</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.06425271339395745</v>
+        <v>0.06357636904244211</v>
       </c>
       <c r="W96">
-        <v>0.2206492101817049</v>
+        <v>0.2208086921797922</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3119063756988226</v>
+        <v>0.3086231506914666</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9211,22 +9211,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2371595977542184</v>
+        <v>0.2390595977542184</v>
       </c>
       <c r="C97">
-        <v>-2265.59703457845</v>
+        <v>-2300.804447077517</v>
       </c>
       <c r="D97">
-        <v>493.1129654215497</v>
+        <v>488.4835529224826</v>
       </c>
       <c r="E97">
-        <v>2125.81</v>
+        <v>2156.388</v>
       </c>
       <c r="F97">
-        <v>2904.91</v>
+        <v>2935.488</v>
       </c>
       <c r="G97">
         <v>146.2</v>
@@ -9247,37 +9247,37 @@
         <v>211.3999999999999</v>
       </c>
       <c r="M97">
-        <v>684.9777779999999</v>
+        <v>692.1880704</v>
       </c>
       <c r="N97">
-        <v>-473.577778</v>
+        <v>-480.7880704000001</v>
       </c>
       <c r="O97">
-        <v>-97.55702226800001</v>
+        <v>-99.04234250240003</v>
       </c>
       <c r="P97">
-        <v>-376.020755732</v>
+        <v>-381.7457278976001</v>
       </c>
       <c r="Q97">
-        <v>-94.42075573199998</v>
+        <v>-100.1457278976001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.5478268036683164</v>
+        <v>0.6733335045853956</v>
       </c>
       <c r="T97">
-        <v>11.59415250966089</v>
+        <v>14.49269063707611</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.06357636904244211</v>
+        <v>0.06291411519825001</v>
       </c>
       <c r="W97">
-        <v>0.2208086921797922</v>
+        <v>0.2209648516362527</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3086231506914666</v>
+        <v>0.3054083262050971</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9293,22 +9293,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2390595977542183</v>
+        <v>0.2409595977542183</v>
       </c>
       <c r="C98">
-        <v>-2300.804447077518</v>
+        <v>-2335.925744907481</v>
       </c>
       <c r="D98">
-        <v>488.4835529224823</v>
+        <v>483.9402550925184</v>
       </c>
       <c r="E98">
-        <v>2156.388</v>
+        <v>2186.966</v>
       </c>
       <c r="F98">
-        <v>2935.488</v>
+        <v>2966.066</v>
       </c>
       <c r="G98">
         <v>146.2</v>
@@ -9329,37 +9329,37 @@
         <v>211.3999999999999</v>
       </c>
       <c r="M98">
-        <v>692.1880704</v>
+        <v>699.3983628</v>
       </c>
       <c r="N98">
-        <v>-480.7880704000001</v>
+        <v>-487.9983628000001</v>
       </c>
       <c r="O98">
-        <v>-99.04234250240003</v>
+        <v>-100.5276627368</v>
       </c>
       <c r="P98">
-        <v>-381.7457278976001</v>
+        <v>-387.4707000632</v>
       </c>
       <c r="Q98">
-        <v>-100.1457278976001</v>
+        <v>-105.8707000632</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.673333504585394</v>
+        <v>0.882511339447192</v>
       </c>
       <c r="T98">
-        <v>14.49269063707608</v>
+        <v>19.32358751610143</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.06291411519825001</v>
+        <v>0.06226551607249486</v>
       </c>
       <c r="W98">
-        <v>0.2209648516362527</v>
+        <v>0.2211177913101057</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3054083262050971</v>
+        <v>0.3022597867596838</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9375,22 +9375,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2409595977542183</v>
+        <v>0.2428595977542183</v>
       </c>
       <c r="C99">
-        <v>-2335.925744907481</v>
+        <v>-2370.9633087374</v>
       </c>
       <c r="D99">
-        <v>483.9402550925184</v>
+        <v>479.4806912626</v>
       </c>
       <c r="E99">
-        <v>2186.966</v>
+        <v>2217.544</v>
       </c>
       <c r="F99">
-        <v>2966.066</v>
+        <v>2996.644</v>
       </c>
       <c r="G99">
         <v>146.2</v>
@@ -9411,37 +9411,37 @@
         <v>211.3999999999999</v>
       </c>
       <c r="M99">
-        <v>699.3983628</v>
+        <v>706.6086551999999</v>
       </c>
       <c r="N99">
-        <v>-487.9983628000001</v>
+        <v>-495.2086552</v>
       </c>
       <c r="O99">
-        <v>-100.5276627368</v>
+        <v>-102.0129829712</v>
       </c>
       <c r="P99">
-        <v>-387.4707000632</v>
+        <v>-393.1956722288</v>
       </c>
       <c r="Q99">
-        <v>-105.8707000632</v>
+        <v>-111.5956722288</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.882511339447192</v>
+        <v>1.300867009170788</v>
       </c>
       <c r="T99">
-        <v>19.32358751610143</v>
+        <v>28.98538127415215</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.06226551607249486</v>
+        <v>0.06163015366359185</v>
       </c>
       <c r="W99">
-        <v>0.2211177913101057</v>
+        <v>0.2212676097661251</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3022597867596838</v>
+        <v>0.2991755032213197</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9457,22 +9457,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2428595977542183</v>
+        <v>0.2447595977542183</v>
       </c>
       <c r="C100">
-        <v>-2370.9633087374</v>
+        <v>-2405.919432285064</v>
       </c>
       <c r="D100">
-        <v>479.4806912626</v>
+        <v>475.1025677149361</v>
       </c>
       <c r="E100">
-        <v>2217.544</v>
+        <v>2248.122</v>
       </c>
       <c r="F100">
-        <v>2996.644</v>
+        <v>3027.222</v>
       </c>
       <c r="G100">
         <v>146.2</v>
@@ -9493,37 +9493,37 @@
         <v>211.3999999999999</v>
       </c>
       <c r="M100">
-        <v>706.6086551999999</v>
+        <v>713.8189476</v>
       </c>
       <c r="N100">
-        <v>-495.2086552</v>
+        <v>-502.4189476000001</v>
       </c>
       <c r="O100">
-        <v>-102.0129829712</v>
+        <v>-103.4983032056</v>
       </c>
       <c r="P100">
-        <v>-393.1956722288</v>
+        <v>-398.9206443944</v>
       </c>
       <c r="Q100">
-        <v>-111.5956722288</v>
+        <v>-117.3206443944</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.300867009170788</v>
+        <v>2.555934018341576</v>
       </c>
       <c r="T100">
-        <v>28.98538127415215</v>
+        <v>57.97076254830429</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.06163015366359185</v>
+        <v>0.0610076268589091</v>
       </c>
       <c r="W100">
-        <v>0.2212676097661251</v>
+        <v>0.2214144015866692</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9531,91 +9531,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2991755032213197</v>
+        <v>0.2961535284413063</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2447595977542183</v>
-      </c>
-      <c r="C101">
-        <v>-2405.919432285064</v>
-      </c>
-      <c r="D101">
-        <v>475.1025677149361</v>
-      </c>
-      <c r="E101">
-        <v>2248.122</v>
-      </c>
-      <c r="F101">
-        <v>3027.222</v>
-      </c>
-      <c r="G101">
-        <v>146.2</v>
-      </c>
-      <c r="H101">
-        <v>2278.7</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>492.9999999999999</v>
-      </c>
-      <c r="K101">
-        <v>281.6</v>
-      </c>
-      <c r="L101">
-        <v>211.3999999999999</v>
-      </c>
-      <c r="M101">
-        <v>713.8189476</v>
-      </c>
-      <c r="N101">
-        <v>-502.4189476000001</v>
-      </c>
-      <c r="O101">
-        <v>-103.4983032056</v>
-      </c>
-      <c r="P101">
-        <v>-398.9206443944</v>
-      </c>
-      <c r="Q101">
-        <v>-117.3206443944</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.555934018341576</v>
-      </c>
-      <c r="T101">
-        <v>57.97076254830429</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.0610076268589091</v>
-      </c>
-      <c r="W101">
-        <v>0.2214144015866692</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.2961535284413063</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
